--- a/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>IPG</t>
   </si>
@@ -656,306 +656,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3023300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2678500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2666500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2521000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2985900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2637700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2735700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2568500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2932100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2542000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2509600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2257000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2550000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2125500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2025700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2359800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2901800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2438100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2520200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2361200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2856000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2297500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2391800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2169100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2589800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2208200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2185800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2063800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2264500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1922200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2326900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2219400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2277100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2251700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2337600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2216200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2300200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2229100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2354200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2092400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2025900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1915300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1976600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1748700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1795400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2188700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2320600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2079000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2162800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2166700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2247000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1970200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2069800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2049200</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>5</v>
@@ -972,82 +978,85 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>696400</v>
+      </c>
+      <c r="E10" s="3">
         <v>459100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>389400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>269300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>648300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>421500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>435500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>339400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>577900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>449600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>483700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>341700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>573400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>376800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>230300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>171100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>581200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>359100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>357400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>194500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>609000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>327300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>322000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>119900</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>5</v>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,192 +1298,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E14" s="3">
         <v>11500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>109000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-8900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>87800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>269100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>55900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>132500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>19800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>24400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>8700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>13100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>25100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E15" s="3">
         <v>66000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>66500</v>
       </c>
       <c r="F15" s="3">
         <v>66500</v>
       </c>
       <c r="G15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="H15" s="3">
         <v>72100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>67000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>67100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>67800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>75100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>69400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>70100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>69200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>73700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>71000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>73100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>72800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>65400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>69000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>73000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>71100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>68900</v>
-      </c>
-      <c r="X15" s="3">
-        <v>44000</v>
       </c>
       <c r="Y15" s="3">
         <v>44000</v>
       </c>
       <c r="Z15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>46000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>32600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>42200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>41300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2379700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2313800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2358400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2336900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2548600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2292800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2387300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2329200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2475600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2194900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2126900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2100500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2341800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1885500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2005100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2307200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2434400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2165500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2259200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2319600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2408800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2041600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2162400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2154700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2170000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1961900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1973200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2028200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1804500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1711100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>643600</v>
+      </c>
+      <c r="E18" s="3">
         <v>364700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>308100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>184100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>437300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>344900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>348400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>239300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>456500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>347100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>382700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>156500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>208200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>240000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>52600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>467400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>272600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>261000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>41600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>447200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>255900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>229400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>419800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>246300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>212600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>35600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>460000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>211100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E20" s="3">
         <v>33500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>33700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>37700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>24900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>31400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>9800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>7100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>750600</v>
+      </c>
+      <c r="E21" s="3">
         <v>464200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>408300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>288300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>534300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>443300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>422900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>317100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>546400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>430600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>466800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>235200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>294100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>314400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>98000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>137600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>541400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>351400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>341100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>122200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>522200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>295700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>281600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>64400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>459300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>291400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>256300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>81700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>505600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>257700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E22" s="3">
         <v>58700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>63200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>55800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>49400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>44900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>41000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>39400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>38000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>42900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>42600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>49600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>46800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>49800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>44800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>49700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>51600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>49800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>49400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>27600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>21000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>20900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>21800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>623900</v>
+      </c>
+      <c r="E23" s="3">
         <v>339500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>278600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>166000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>412800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>331400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>314800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>209900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>433300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>318300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>354100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>116400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>173600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>192600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>427800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>232700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>216500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>403900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>224100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>211500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>403500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>228200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>189300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>19800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>441100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>155300</v>
+      </c>
+      <c r="E24" s="3">
         <v>91500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>109200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>76400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>83700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>49100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>67400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>86700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>58100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-86300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>17200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>86100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>64600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>43600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>62200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>60700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>63600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>135100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>54900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>81600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>106100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>468600</v>
+      </c>
+      <c r="E26" s="3">
         <v>248000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>268000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>132200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>303600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>255000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>231100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>160800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>365900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>244400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>267400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>92600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>115500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>278900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-43900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>341700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>168100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>172900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>341700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>163400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>147900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>268400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>173300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>107700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>335000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>463200</v>
+      </c>
+      <c r="E27" s="3">
         <v>243700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>265500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>126000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>297200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>251800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>229600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>159400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>357900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>239900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>263300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>91700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>112300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>279700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-45600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>328900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>165600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>169500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>326200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>161000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>145800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>252300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>169700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>107700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>24700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>317600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,8 +2659,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2617,11 +2677,11 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>36000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-33500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-33700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-37700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-24900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-31400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-9800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-7100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>463200</v>
+      </c>
+      <c r="E33" s="3">
         <v>243700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>265500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>126000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>297200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>251800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>229600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>159400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>357900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>239900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>263300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>91700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>112300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>279700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-45600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>328900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>165600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>169500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>326200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>161000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>145800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>288300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>169700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>107700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>24700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>317600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>463200</v>
+      </c>
+      <c r="E35" s="3">
         <v>243700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>265500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>126000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>297200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>251800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>229600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>159400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>357900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>239900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>263300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>91700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>112300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>279700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-45600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>328900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>165600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>169500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>326200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>161000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>145800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>288300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>169700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>107700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>24700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>317600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,111 +3437,115 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2386100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1574900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1628100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1678100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2545300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1768300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1983400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2402300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3270000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2490000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2340600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2015300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2509000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1628000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1085400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1554000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1192200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>520500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>614000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>630500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>673400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1860200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>493200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>597300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>790900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>704900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>657600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>775000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1097600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>891600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="3">
         <v>101800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>102800</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>5</v>
@@ -3473,8 +3562,8 @@
       <c r="K42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -3518,118 +3607,124 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
+      <c r="AA42" s="3">
+        <v>0</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>3200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3100</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>3000</v>
       </c>
       <c r="AF42" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7998000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6464300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6385900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5946500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7339000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6279100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6247900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6335200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7524900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6192900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5937000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5283000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6467100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5114600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4610300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5575500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7143300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6066500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6367100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6104900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7027200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6005000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6193500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5923600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6332400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5438400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5482900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5384200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5907800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5558100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,192 +3815,201 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>566300</v>
+      </c>
+      <c r="E45" s="3">
         <v>504400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>524200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>546300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>440900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>487500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>529500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>532500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>436900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>450000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>504900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>471900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>391500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>541700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>518600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>467200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>435200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>463000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>494300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>511600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>482300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>465300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>458900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>442600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>352200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>320500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>342800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>427200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>429600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10950400</v>
+      </c>
+      <c r="E46" s="3">
         <v>8645400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8641000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8170900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10325200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8534900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8760800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9270000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11231800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9132900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8782500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7770200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9367600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7284300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6214300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7596700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8770700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7050000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7475400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7247000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8182900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8330500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7145600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6963500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7475500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6463800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6486500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6589500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7438000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6733200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,192 +4100,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1799300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1809700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1870300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1879400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1914900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2024500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2088000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2161400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2220200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2182800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1994500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2028200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2069600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2260000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2153600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2278200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2352500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2331700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2363600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2122600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>790900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>602900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>602000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>634200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2337000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>637500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>635000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>616300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>622000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>581600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5824500</v>
+      </c>
+      <c r="E49" s="3">
         <v>5818600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5864300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5859300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5868700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5578300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5655000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5724600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5756200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5784100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5837000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5847900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5879100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5824700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5810500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5817200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5908700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5879700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5936100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5959700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5970700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3784700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3788100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3820400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3753100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3703500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3674400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3715300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>693100</v>
+      </c>
+      <c r="E52" s="3">
         <v>753600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>734400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>754500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>736200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>737500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>745400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>724900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>701000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>705500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>707700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>703400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>726400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>705700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>718500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>736800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>720000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>736200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>751800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>720700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>675800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>795000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>821900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>802700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>758400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>814900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>803600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>788600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>750800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>809400</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19267300</v>
+      </c>
+      <c r="E54" s="3">
         <v>17027300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17110000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16664100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18845000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16875200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17249200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17880900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19909200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17805300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17321700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16349700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18042700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16074700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14896900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16428900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17751900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15997600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16526900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16050000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15620300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13513100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12357600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12240100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12704700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11716100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11678200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11697900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12485200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11839500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8355000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6448400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6573200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6460600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8235300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6535600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6861300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7245300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8960000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6844200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6605900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5862000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7269700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5105900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4328100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5559500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7205400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5656000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6022300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5733700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6698100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5515100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5738800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5467100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6420200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5561100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5872000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5672600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6303600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6025900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>284300</v>
+      </c>
+      <c r="E58" s="3">
         <v>281000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>280500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>28300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>44900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>56400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>46300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>59700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>48200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>544500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>559800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>545900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>550500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>552900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>554900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>812600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>554400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>248100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>207400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>272500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>73800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>82700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>757700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>801500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>86900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>813700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>539400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>634900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>409600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1691600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1596800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1501600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1471100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1703000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1577200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1555100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1649200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1881800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1660300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1631000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1576600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1760300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1569100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1483500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1423800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1660600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1494300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1501600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1524900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1352000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1093900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1088800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1053900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1168200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>571500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>534800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>683200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>992800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>631700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10330900</v>
+      </c>
+      <c r="E60" s="3">
         <v>8326200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8355300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7960000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9983200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8169200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8462700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8954200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10890000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9049000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8796700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7984500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9580500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7227900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6366500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7795900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9420400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7398400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7731300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7531100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8123900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6691700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7585300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7322500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7675300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6946300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6946200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6990700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7706000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6815100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2917500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2916200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2915400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2871500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2870700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2902500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2906100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2908100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2908600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2908300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2907900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2906900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2915800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3411300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3411700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3410900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2771900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3367100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3563800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3663700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3660200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3261400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1282700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1288200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1285600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1285000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1283100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1281900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1280700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1583300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1972800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2007200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2048000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2174200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2246800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2337300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2382000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2461900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2505800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2554100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2433600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2451500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2509400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2522100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2472400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2492100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2569300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2543600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2585100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2338800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1235500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1230100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1232200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1242200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1245400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1206600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1193200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1187700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1189000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1218700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15324700</v>
+      </c>
+      <c r="E66" s="3">
         <v>13347100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13423700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13104800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15197100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13470600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13812500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14393900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16383200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14633900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14258800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13475700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15147700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13352100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12446500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13896400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14976000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13528600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14103000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13734700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13227100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11375200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10295900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10131600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10493200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9702700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9695700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9734900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10468100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9898100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4254500</v>
+      </c>
+      <c r="E72" s="3">
         <v>3911100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3782800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3638100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3632100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3449900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3311800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3196700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3154300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2908900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2777500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2623100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2636900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2623400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2444300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2591100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2689900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2455500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2381800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2303100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2400100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2158400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2076700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2010500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2104500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1849800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1774900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1751200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1804300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1546600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3942600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3680200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3686300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3559300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3647900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3404600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3436700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3487000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3526000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3171400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3062900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2874000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2895000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2722600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2450400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2532500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2775900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2469000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2423900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2315300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2393200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2137900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2061700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2108500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2211500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2013400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1982500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1963000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2017100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1941400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>463200</v>
+      </c>
+      <c r="E81" s="3">
         <v>243700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>265500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>126000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>297200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>251800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>229600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>159400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>357900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>239900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>263300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>91700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>112300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>279700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-45600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>328900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>165600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>169500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>326200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>161000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>145800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>288300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>169700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>107700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>24700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>317600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E83" s="3">
         <v>66000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>66500</v>
       </c>
       <c r="F83" s="3">
         <v>66500</v>
       </c>
       <c r="G83" s="3">
+        <v>66500</v>
+      </c>
+      <c r="H83" s="3">
         <v>72100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>67000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>67100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>67800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>75100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>69400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>70100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>69200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>73700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>71000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>73100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>72800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>65400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>69000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>73000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>71100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>68900</v>
-      </c>
-      <c r="X83" s="3">
-        <v>44000</v>
       </c>
       <c r="Y83" s="3">
         <v>44000</v>
       </c>
       <c r="Z83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>46000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>42200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>41300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>42700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>894800</v>
+      </c>
+      <c r="E89" s="3">
         <v>242700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-35200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-547600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1267600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>65600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-90800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-633600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1467000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>390200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>468200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-249800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1522100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>689300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-87100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-277100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1105600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>224600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>292500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-93500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>891800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>231000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>172200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-729900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1020800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>14100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>218700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-371800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>540300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>527700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-32900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-46200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-61300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-55500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-40100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-44600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-64700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-53700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-47300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-32800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-71400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-44200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-38700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>28300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-48600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-121000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-34700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-303900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-36400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-61000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-70200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-72000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-83700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-39200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-32500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-60800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-41000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-47200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-30700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2374900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-59000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-55700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-44500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-33200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-96400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,100 +8117,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-117900</v>
+      </c>
+      <c r="E96" s="3">
         <v>-118600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-119400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-123200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-112200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-113000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-113800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-118300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-106300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-106200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-106100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-109100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-99500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-99400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-99200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-100000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-90900</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-90800</v>
       </c>
       <c r="U96" s="3">
         <v>-90800</v>
       </c>
       <c r="V96" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="W96" s="3">
         <v>-90600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-80500</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-80400</v>
       </c>
       <c r="Y96" s="3">
         <v>-80400</v>
       </c>
       <c r="Z96" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-69100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-69800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-70500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-59500</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-244300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-225500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>109800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-274300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-246500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-209800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-233000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-210100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-616400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-153300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-101800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-212700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-608500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-115400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-366700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>744400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-398000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-253300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-278400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>86700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>302600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1209600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-217200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>558200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-891800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>86300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-263800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>64400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-207400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-233700</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>60800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-30400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-33800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-30400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>51300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>17800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-46700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-21400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>16700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-12000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>16400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>20000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-39100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>811400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-52700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-50400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-866300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>778000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-211000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-418600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-867500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>775300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>152500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>325600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-492700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>881200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>543300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-468500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>359800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>671700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-92900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-43900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1192500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1373800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-104100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-197700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>89700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>48100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-320600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>205300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>219700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>IPG</t>
   </si>
@@ -656,315 +656,322 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2495900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3023300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2678500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2666500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2521000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2985900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2637700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2735700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2568500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2932100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2542000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2509600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2257000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2550000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2125500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2025700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2359800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2901800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2438100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2520200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2361200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2856000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2297500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2391800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2169100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2589800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2208200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2185800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2063800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2264500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1922200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2207900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2326900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2219400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2277100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2251700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2337600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2216200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2300200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2229100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2354200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2092400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2025900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1915300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1976600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1748700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1795400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2188700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2320600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2079000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2162800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2166700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2247000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1970200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2069800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2049200</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>5</v>
@@ -981,85 +988,88 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>288000</v>
+      </c>
+      <c r="E10" s="3">
         <v>696400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>459100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>389400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>269300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>648300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>421500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>435500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>339400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>577900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>449600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>483700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>341700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>573400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>376800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>230300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>171100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>581200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>359100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>357400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>194500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>609000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>327300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>322000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>119900</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>5</v>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,198 +1318,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-36000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>11500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>109000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-8900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>87800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>269100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>55900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>132500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>40400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>19800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>24400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>8700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>13100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>25100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E15" s="3">
         <v>65300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>66000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>66500</v>
       </c>
       <c r="G15" s="3">
         <v>66500</v>
       </c>
       <c r="H15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="I15" s="3">
         <v>72100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>67000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>67100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>67800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>75100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>69400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>70100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>69200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>73700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>71000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>73100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>72800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>65400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>69000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>73000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>71100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>68900</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>44000</v>
       </c>
       <c r="Z15" s="3">
         <v>44000</v>
       </c>
       <c r="AA15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>46000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>32600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>42200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>41300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2318500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2379700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2313800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2358400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2336900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2548600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2292800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2387300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2329200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2475600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2194900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2126900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2100500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2341800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1885500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2005100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2307200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2434400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2165500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2259200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2319600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2408800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2041600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2162400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2154700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2170000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1961900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1973200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2028200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1804500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1711100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>177400</v>
+      </c>
+      <c r="E18" s="3">
         <v>643600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>364700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>308100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>184100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>437300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>344900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>348400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>239300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>456500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>347100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>382700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>156500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>208200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>240000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>52600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>467400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>272600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>261000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>41600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>447200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>255900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>229400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>419800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>246300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>212600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>35600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>460000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>211100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E20" s="3">
         <v>41700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>33500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>33700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>37700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>24900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>31400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>12200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>288600</v>
+      </c>
+      <c r="E21" s="3">
         <v>750600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>464200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>408300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>288300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>534300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>443300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>422900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>317100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>546400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>430600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>466800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>235200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>294100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>314400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>98000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>137600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>541400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>351400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>341100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>122200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>522200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>295700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>281600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>64400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>459300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>291400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>256300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>81700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>505600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>257700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E22" s="3">
         <v>61400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>58700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>63200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>55800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>49400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>44900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>41000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>38000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>42900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>42600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>49600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>46800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>50800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>49800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>44800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>48200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>49700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>51600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>49800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>49400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>27600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>26100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>21000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>20900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>160600</v>
+      </c>
+      <c r="E23" s="3">
         <v>623900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>339500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>278600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>166000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>412800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>331400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>314800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>209900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>433300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>318300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>354100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>116400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>173600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>192600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>427800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>232700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>216500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>403900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>224100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>211500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>403500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>228200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>189300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>19800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>441100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E24" s="3">
         <v>155300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>91500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>33800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>109200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>76400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>83700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>49100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>67400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>73900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>86700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>58100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-86300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>86100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>64600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>62200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>60700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>63600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>135100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>54900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>81600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>106100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E26" s="3">
         <v>468600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>248000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>268000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>132200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>303600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>255000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>231100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>160800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>365900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>244400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>267400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>92600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>115500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>278900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-43900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>341700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>168100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>172900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>341700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>163400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>147900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>268400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>173300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>107700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>335000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E27" s="3">
         <v>463200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>243700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>265500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>126000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>297200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>251800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>229600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>159400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>357900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>239900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>263300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>91700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>112300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>279700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>328900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>165600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>169500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>326200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>161000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>145800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>252300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>169700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>107700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>24700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>317600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2662,8 +2723,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2680,11 +2741,11 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>36000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-41700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-33500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-33700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-37700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-24900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-31400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-12200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E33" s="3">
         <v>463200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>243700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>265500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>126000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>297200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>251800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>229600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>159400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>357900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>239900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>263300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>91700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>112300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>279700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>328900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>165600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>169500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>326200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>161000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>145800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>288300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>169700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>107700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>24700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>317600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E35" s="3">
         <v>463200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>243700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>265500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>126000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>297200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>251800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>229600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>159400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>357900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>239900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>263300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>91700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>112300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>279700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>328900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>165600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>169500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>326200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>161000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>145800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>288300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>169700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>107700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>24700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>317600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,117 +3524,121 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1931200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2386100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1574900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1628100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1678100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2545300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1768300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1983400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2402300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3270000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2490000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2340600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2015300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2509000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1628000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1085400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1554000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1192200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>520500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>614000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>630500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>673400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1860200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>493200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>597300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>790900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>704900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>657600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>775000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1097600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>891600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3">
         <v>101800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>102800</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>5</v>
@@ -3565,8 +3655,8 @@
       <c r="L42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -3610,121 +3700,127 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
+      <c r="AB42" s="3">
+        <v>0</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3">
         <v>3200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3100</v>
-      </c>
-      <c r="AF42" s="3">
-        <v>3000</v>
       </c>
       <c r="AG42" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6474600</v>
+      </c>
+      <c r="E43" s="3">
         <v>7998000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6464300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6385900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5946500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7339000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6279100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6247900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6335200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7524900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6192900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5937000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5283000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6467100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5114600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4610300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5575500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7143300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6066500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6367100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6104900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7027200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6005000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6193500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5923600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6332400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5438400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5482900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5384200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5907800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5558100</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,198 +3914,207 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>620100</v>
+      </c>
+      <c r="E45" s="3">
         <v>566300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>504400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>524200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>546300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>440900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>487500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>529500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>532500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>436900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>450000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>504900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>471900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>391500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>541700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>518600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>467200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>435200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>463000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>494300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>511600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>482300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>465300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>458900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>442600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>352200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>320500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>342800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>427200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>429600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9025900</v>
+      </c>
+      <c r="E46" s="3">
         <v>10950400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8645400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8641000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8170900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10325200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8534900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8760800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9270000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11231800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9132900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8782500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7770200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9367600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7284300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6214300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7596700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8770700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7050000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7475400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7247000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8182900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8330500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7145600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6963500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7475500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6463800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6486500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6589500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7438000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6733200</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1755100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1799300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1809700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1870300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1879400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1914900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2024500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2088000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2161400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2220200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2182800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1994500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2028200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2069600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2260000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2153600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2278200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2352500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2331700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2363600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2122600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>790900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>602900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>602000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>634200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2337000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>637500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>635000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>616300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>622000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>581600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5786000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5824500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5818600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5864300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5859300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5868700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5578300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5655000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5724600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5756200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5784100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5837000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5847900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5879100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5824700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5810500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5817200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5908700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5879700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5936100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5959700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5970700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3784700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3788100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3820400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3753100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3703500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3674400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3715300</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>719100</v>
+      </c>
+      <c r="E52" s="3">
         <v>693100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>753600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>734400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>754500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>736200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>737500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>745400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>724900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>701000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>705500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>707700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>703400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>726400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>705700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>718500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>736800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>720000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>736200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>751800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>720700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>675800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>795000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>821900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>802700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>758400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>814900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>803600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>788600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>750800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>809400</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17286100</v>
+      </c>
+      <c r="E54" s="3">
         <v>19267300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17027300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17110000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16664100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18845000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16875200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17249200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17880900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19909200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17805300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17321700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16349700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18042700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16074700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14896900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16428900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17751900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15997600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16526900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16050000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15620300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13513100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12357600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12240100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12704700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11716100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11678200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11697900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12485200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11839500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6729700</v>
+      </c>
+      <c r="E57" s="3">
         <v>8355000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6448400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6573200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6460600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8235300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6535600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6861300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7245300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8960000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6844200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6605900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5862000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7269700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5105900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4328100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5559500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7205400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5656000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6022300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5733700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6698100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5515100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5738800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5467100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6420200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5561100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5872000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5672600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6303600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6025900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>272100</v>
+      </c>
+      <c r="E58" s="3">
         <v>284300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>281000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>280500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>28300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>44900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>56400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>46300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>59700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>48200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>544500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>559800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>545900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>550500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>552900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>554900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>812600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>554400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>248100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>207400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>272500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>73800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>82700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>757700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>801500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>86900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>813700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>539400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>634900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>409600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1496500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1691600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1596800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1501600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1471100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1703000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1577200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1555100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1649200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1881800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1660300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1631000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1576600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1760300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1569100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1483500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1423800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1660600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1494300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1501600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1524900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1352000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1093900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1088800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1053900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1168200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>571500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>534800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>683200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>992800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>631700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8498300</v>
+      </c>
+      <c r="E60" s="3">
         <v>10330900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8326200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8355300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7960000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9983200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8169200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8462700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8954200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10890000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9049000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8796700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7984500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9580500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7227900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6366500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7795900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9420400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7398400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7731300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7531100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8123900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6691700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7585300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7322500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7675300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6946300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6946200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6990700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7706000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6815100</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2918400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2917500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2916200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2915400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2871500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2870700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2902500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2906100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2908100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2908600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2908300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2907900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2906900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2915800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3411300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3411700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3410900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2771900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3367100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3563800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3663700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3660200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3261400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1282700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1288200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1285600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1285000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1283100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1281900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1280700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1583300</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1950300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1972800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2007200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2048000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2174200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2246800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2337300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2382000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2461900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2505800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2554100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2433600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2451500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2509400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2522100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2472400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2492100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2569300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2543600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2585100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2338800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1235500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1230100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1232200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1242200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1245400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1206600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1193200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1187700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1189000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1218700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13462000</v>
+      </c>
+      <c r="E66" s="3">
         <v>15324700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13347100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13423700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13104800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15197100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13470600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13812500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14393900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16383200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14633900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14258800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13475700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15147700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13352100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12446500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13896400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14976000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13528600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14103000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13734700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13227100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11375200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10295900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10131600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10493200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9702700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9695700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9734900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10468100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9898100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4239100</v>
+      </c>
+      <c r="E72" s="3">
         <v>4254500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3911100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3782800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3638100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3632100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3449900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3311800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3196700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3154300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2908900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2777500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2623100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2636900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2623400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2444300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2591100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2689900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2455500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2381800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2303100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2400100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2158400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2076700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2010500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2104500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1849800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1774900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1751200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1804300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1546600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3824100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3942600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3680200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3686300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3559300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3647900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3404600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3436700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3487000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3526000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3171400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3062900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2874000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2895000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2722600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2450400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2532500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2775900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2469000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2423900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2315300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2393200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2137900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2061700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2108500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2211500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2013400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1982500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1963000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2017100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1941400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E81" s="3">
         <v>463200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>243700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>265500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>126000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>297200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>251800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>229600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>159400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>357900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>239900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>263300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>91700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>112300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>279700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>328900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>165600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>169500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>326200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>161000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>145800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>288300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>169700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>107700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>24700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>317600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E83" s="3">
         <v>65300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>66000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>66500</v>
       </c>
       <c r="G83" s="3">
         <v>66500</v>
       </c>
       <c r="H83" s="3">
+        <v>66500</v>
+      </c>
+      <c r="I83" s="3">
         <v>72100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>67000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>67100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>75100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>69400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>70100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>69200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>73700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>71000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>73100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>72800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>65400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>69000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>73000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>71100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>68900</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>44000</v>
       </c>
       <c r="Z83" s="3">
         <v>44000</v>
       </c>
       <c r="AA83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>46000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>42200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>42700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-157400</v>
+      </c>
+      <c r="E89" s="3">
         <v>894800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>242700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-35200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-547600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1267600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>65600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-90800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-633600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1467000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>390200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>468200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-249800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1522100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>689300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-87100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-277100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1105600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>224600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>292500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-93500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>891800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>231000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>172200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-729900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1020800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>14100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>218700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-371800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>540300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>527700</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-52200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-41600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-61300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-40100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-44600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-64700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-53700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-47300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-32800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-71400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-44200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>28300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E94" s="3">
         <v>118900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-48600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-121000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-34700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-303900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-61000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-70200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-72000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-83700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-32500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-60800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-41000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-42800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-47200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-30700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2374900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-59000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-44500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-33200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-96400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,103 +8351,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-126600</v>
+      </c>
+      <c r="E96" s="3">
         <v>-117900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-118600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-119400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-123200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-112200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-113000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-113800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-118300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-106300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-106200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-106100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-109100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-99500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-99400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-99200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-100000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-90900</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-90800</v>
       </c>
       <c r="V96" s="3">
         <v>-90800</v>
       </c>
       <c r="W96" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="X96" s="3">
         <v>-90600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-80500</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-80400</v>
       </c>
       <c r="Z96" s="3">
         <v>-80400</v>
       </c>
       <c r="AA96" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-69100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-69800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-70500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-59500</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-227100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-244300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-225500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>109800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-274300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-246500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-209800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-233000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-210100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-616400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-153300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-101800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-212700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-608500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-115400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-366700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>744400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-398000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-253300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-278400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>86700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>302600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1209600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-217200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>558200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-891800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>86300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-263800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>64400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-207400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-233700</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E101" s="3">
         <v>42000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-21300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>60800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-30400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-33800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-12400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-30400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>51300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>17800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-46700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-21400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>16700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-24600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>16400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>20000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-39100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-454500</v>
+      </c>
+      <c r="E102" s="3">
         <v>811400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-52700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-50400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-866300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>778000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-211000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-418600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-867500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>775300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>152500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>325600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-492700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>881200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>543300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-468500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>359800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>671700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-92900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-43900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1192500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1373800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-104100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-197700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>89700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>48100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-320600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>205300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>219700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>IPG</t>
   </si>
@@ -656,325 +656,332 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2710000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2495900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3023300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2678500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2666500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2521000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2985900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2637700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2735700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2568500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2932100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2542000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2509600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2257000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2550000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2125500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2025700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2359800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2901800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2438100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2520200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2361200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2856000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2297500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2391800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2169100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2589800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2208200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2185800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2063800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2264500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1922200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2298900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2207900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2326900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2219400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2277100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2251700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2337600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2216200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2300200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2229100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2354200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2092400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2025900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1915300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1976600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1748700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1795400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2188700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2320600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2079000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2162800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2166700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2247000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1970200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2069800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2049200</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>5</v>
@@ -991,88 +998,91 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>411100</v>
+      </c>
+      <c r="E10" s="3">
         <v>288000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>696400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>459100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>389400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>269300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>648300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>421500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>435500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>339400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>577900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>449600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>483700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>341700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>573400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>376800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>230300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>171100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>581200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>359100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>357400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>194500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>609000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>327300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>322000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>119900</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>5</v>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,204 +1338,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E14" s="3">
         <v>7400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-36000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>109000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-8900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>87800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>269100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>55900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>132500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>40400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>11900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>19800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>24400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>13100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>25100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E15" s="3">
         <v>65200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>65300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>66000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>66500</v>
       </c>
       <c r="H15" s="3">
         <v>66500</v>
       </c>
       <c r="I15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="J15" s="3">
         <v>72100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>67000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>67100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>67800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>75100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>69400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>70100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>69200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>73700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>71000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>73100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>72800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>65400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>69000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>73000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>71100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>68900</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>44000</v>
       </c>
       <c r="AA15" s="3">
         <v>44000</v>
       </c>
       <c r="AB15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>46000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>32600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>42200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>41300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2389700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2318500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2379700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2313800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2358400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2336900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2548600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2292800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2387300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2329200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2475600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2194900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2126900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2341800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1885500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2005100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2307200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2434400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2165500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2259200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2319600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2408800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2041600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2162400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2154700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2170000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1961900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1973200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2028200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1804500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1711100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>320300</v>
+      </c>
+      <c r="E18" s="3">
         <v>177400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>643600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>364700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>308100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>184100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>437300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>344900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>348400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>239300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>456500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>347100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>382700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>156500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>208200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>240000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>52600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>467400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>272600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>261000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>41600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>447200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>255900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>229400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>419800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>246300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>212600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>35600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>460000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>211100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E20" s="3">
         <v>46000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>41700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>33500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>33700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>37700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>24900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>31400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>9500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>8200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>418600</v>
+      </c>
+      <c r="E21" s="3">
         <v>288600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>750600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>464200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>408300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>288300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>534300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>443300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>422900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>317100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>546400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>430600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>466800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>235200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>294100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>314400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>98000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>137600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>541400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>351400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>341100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>122200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>522200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>295700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>281600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>64400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>459300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>291400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>256300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>81700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>505600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>257700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E22" s="3">
         <v>62800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>61400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>58700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>63200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>55800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>49400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>44900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>38000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>42900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>42600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>49600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>46800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>49800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>44800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>49700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>51600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>49800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>49400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>27600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>26100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>21000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>21800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>295700</v>
+      </c>
+      <c r="E23" s="3">
         <v>160600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>623900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>339500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>278600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>166000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>412800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>331400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>314800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>209900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>433300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>318300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>354100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>116400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>173600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>192600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-24900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>427800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>232700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>216500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>403900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>224100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>211500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>403500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>228200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>189300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>19800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>441100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>75600</v>
+      </c>
+      <c r="E24" s="3">
         <v>47300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>155300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>91500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>109200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>76400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>83700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>49100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>67400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>73900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>86700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>58100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-86300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>17200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>86100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>64600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>43600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>62200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>60700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>63600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>135100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>54900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>81600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>106100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>220100</v>
+      </c>
+      <c r="E26" s="3">
         <v>113300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>468600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>248000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>268000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>132200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>303600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>255000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>231100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>160800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>365900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>244400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>267400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>92600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>115500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>278900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-43900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>341700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>168100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>172900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>341700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>163400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>147900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>268400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>173300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>107700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>335000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E27" s="3">
         <v>110400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>463200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>243700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>265500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>126000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>297200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>251800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>229600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>159400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>357900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>239900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>263300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>91700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>112300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>279700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-45600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>328900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>165600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>169500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>326200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>161000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>145800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>252300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>169700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>107700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>24700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>317600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,8 +2787,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2744,11 +2805,11 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>36000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-46000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-41700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-33500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-33700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-37700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-24900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-31400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E33" s="3">
         <v>110400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>463200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>243700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>265500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>126000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>297200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>251800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>229600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>159400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>357900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>239900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>263300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>91700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>112300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>279700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-45600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>328900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>165600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>169500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>326200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>161000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>145800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>288300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>169700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>107700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>24700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>317600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E35" s="3">
         <v>110400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>463200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>243700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>265500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>126000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>297200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>251800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>229600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>159400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>357900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>239900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>263300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>91700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>112300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>279700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-45600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>328900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>165600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>169500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>326200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>161000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>145800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>288300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>169700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>107700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>24700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>317600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1545500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1931200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2386100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1574900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1628100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1678100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2545300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1768300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1983400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2402300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3270000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2490000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2340600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2015300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2509000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1628000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1085400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1554000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1192200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>520500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>614000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>630500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>673400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1860200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>493200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>597300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>790900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>704900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>657600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>775000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1097600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>891600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3634,14 +3724,14 @@
       <c r="E42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="3">
         <v>101800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>102800</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>5</v>
@@ -3658,8 +3748,8 @@
       <c r="M42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3703,124 +3793,130 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
+      <c r="AC42" s="3">
+        <v>0</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>3200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3100</v>
-      </c>
-      <c r="AG42" s="3">
-        <v>3000</v>
       </c>
       <c r="AH42" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6669800</v>
+      </c>
+      <c r="E43" s="3">
         <v>6474600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7998000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6464300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6385900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5946500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7339000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6279100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6247900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6335200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7524900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6192900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5937000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5283000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6467100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5114600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4610300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5575500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7143300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6066500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6367100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6104900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7027200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6005000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6193500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5923600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6332400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5438400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5482900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5384200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5907800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5558100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>610300</v>
+      </c>
+      <c r="E45" s="3">
         <v>620100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>566300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>504400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>524200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>546300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>440900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>487500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>529500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>532500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>436900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>450000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>504900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>471900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>391500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>541700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>518600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>467200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>435200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>463000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>494300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>511600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>482300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>465300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>458900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>442600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>352200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>320500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>342800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>427200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>429600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8825600</v>
+      </c>
+      <c r="E46" s="3">
         <v>9025900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10950400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8645400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8641000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8170900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10325200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8534900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8760800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9270000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11231800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9132900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8782500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7770200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9367600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7284300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6214300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7596700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8770700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7050000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7475400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7247000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8182900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8330500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7145600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6963500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7475500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6463800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6486500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6589500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7438000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6733200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1713100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1755100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1799300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1809700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1870300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1879400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1914900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2024500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2088000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2161400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2220200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2182800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1994500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2028200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2069600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2260000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2153600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2278200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2352500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2331700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2363600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2122600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>790900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>602900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>602000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>634200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2337000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>637500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>635000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>616300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>622000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>581600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5760600</v>
+      </c>
+      <c r="E49" s="3">
         <v>5786000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5824500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5818600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5864300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5859300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5868700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5578300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5655000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5724600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5756200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5784100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5837000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5847900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5879100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5824700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5810500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5817200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5908700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5879700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5936100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5959700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5970700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3784700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3788100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3820400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3753100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3703500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3674400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3715300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>712500</v>
+      </c>
+      <c r="E52" s="3">
         <v>719100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>693100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>753600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>734400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>754500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>736200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>737500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>745400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>724900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>701000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>705500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>707700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>703400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>726400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>705700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>718500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>736800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>720000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>736200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>751800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>720700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>675800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>795000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>821900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>802700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>758400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>814900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>803600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>788600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>750800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>809400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17011800</v>
+      </c>
+      <c r="E54" s="3">
         <v>17286100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19267300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17027300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17110000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16664100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18845000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16875200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17249200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17880900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19909200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17805300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17321700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16349700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18042700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16074700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14896900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16428900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17751900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15997600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16526900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16050000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15620300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13513100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12357600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12240100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12704700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11716100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11678200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11697900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12485200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11839500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6909300</v>
+      </c>
+      <c r="E57" s="3">
         <v>6729700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8355000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6448400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6573200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6460600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8235300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6535600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6861300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7245300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8960000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6844200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6605900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5862000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7269700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5105900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4328100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5559500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7205400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5656000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6022300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5733700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6698100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5515100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5738800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5467100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6420200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5561100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5872000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5672600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6303600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6025900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E58" s="3">
         <v>272100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>284300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>281000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>280500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>28300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>56400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>59700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>48200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>544500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>559800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>545900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>550500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>552900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>554900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>812600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>554400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>248100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>207400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>272500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>73800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>82700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>757700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>801500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>86900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>813700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>539400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>634900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>409600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1357400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1496500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1691600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1596800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1501600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1471100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1703000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1577200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1555100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1649200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1881800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1660300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1631000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1576600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1760300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1569100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1483500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1423800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1660600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1494300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1501600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1524900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1352000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1093900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1088800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1053900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1168200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>571500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>534800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>683200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>992800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>631700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8287300</v>
+      </c>
+      <c r="E60" s="3">
         <v>8498300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10330900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8326200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8355300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7960000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9983200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8169200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8462700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8954200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10890000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9049000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8796700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7984500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9580500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7227900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6366500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7795900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9420400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7398400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7731300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7531100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8123900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6691700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7585300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7322500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7675300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6946300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6946200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6990700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7706000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6815100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2918800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2918400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2917500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2916200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2915400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2871500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2870700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2902500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2906100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2908100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2908600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2908300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2907900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2906900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2915800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3411300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3411700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3410900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2771900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3367100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3563800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3663700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3660200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3261400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1282700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1288200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1285600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1285000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1283100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1281900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1280700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1583300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1867900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1950300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1972800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2007200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2048000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2174200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2246800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2337300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2382000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2461900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2505800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2554100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2433600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2451500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2509400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2522100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2472400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2492100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2569300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2543600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2585100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2338800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1235500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1230100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1232200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1242200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1245400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1206600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1193200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1187700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1189000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1218700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13176200</v>
+      </c>
+      <c r="E66" s="3">
         <v>13462000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15324700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13347100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13423700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13104800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15197100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13470600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13812500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14393900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16383200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14633900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14258800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13475700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15147700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13352100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12446500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13896400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14976000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13528600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14103000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13734700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13227100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11375200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10295900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10131600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10493200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9702700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9695700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9734900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10468100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9898100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4325100</v>
+      </c>
+      <c r="E72" s="3">
         <v>4239100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4254500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3911100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3782800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3638100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3632100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3449900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3311800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3196700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3154300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2908900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2777500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2623100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2636900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2623400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2444300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2591100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2689900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2455500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2381800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2303100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2400100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2158400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2076700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2010500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2104500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1849800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1774900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1751200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1804300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1546600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3835600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3824100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3942600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3680200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3686300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3559300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3647900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3404600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3436700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3487000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3526000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3171400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3062900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2874000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2895000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2722600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2450400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2532500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2775900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2469000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2423900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2315300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2393200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2137900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2061700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2108500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2211500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2013400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1982500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1963000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2017100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1941400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E81" s="3">
         <v>110400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>463200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>243700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>265500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>126000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>297200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>251800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>229600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>159400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>357900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>239900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>263300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>91700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>112300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>279700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-45600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>328900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>165600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>169500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>326200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>161000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>145800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>288300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>169700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>107700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>24700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>317600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E83" s="3">
         <v>65200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>65300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>66000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>66500</v>
       </c>
       <c r="H83" s="3">
         <v>66500</v>
       </c>
       <c r="I83" s="3">
+        <v>66500</v>
+      </c>
+      <c r="J83" s="3">
         <v>72100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>67000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>67800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>75100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>69400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>70100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>69200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>73700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>71000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>73100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>72800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>65400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>69000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>73000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>71100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>68900</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>44000</v>
       </c>
       <c r="AA83" s="3">
         <v>44000</v>
       </c>
       <c r="AB83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AC83" s="3">
         <v>46000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>32600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>42200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>42700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-157400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>894800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>242700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-547600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1267600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-90800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-633600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1467000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>390200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>468200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-249800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1522100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>689300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-87100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-277100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1105600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>224600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>292500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-93500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>891800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>231000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>172200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-729900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1020800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>14100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>218700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-371800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>540300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>527700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-52200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-47800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-30700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-71900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-61300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-33800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-55500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-40100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-44600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-64700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-53700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-47300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-32800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-71400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>28300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>118900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-48600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-121000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-34700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-303900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-61000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-70200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-72000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-83700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-32500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-60800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-41000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-42800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-47200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2374900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-55700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-33200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-96400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8585,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-123900</v>
+      </c>
+      <c r="E96" s="3">
         <v>-126600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-117900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-118600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-119400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-123200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-112200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-113000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-113800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-118300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-106300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-106200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-106100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-109100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-99500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-99400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-99200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-100000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-90900</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-90800</v>
       </c>
       <c r="W96" s="3">
         <v>-90800</v>
       </c>
       <c r="X96" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-90600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-80500</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-80400</v>
       </c>
       <c r="AA96" s="3">
         <v>-80400</v>
       </c>
       <c r="AB96" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-69100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-69800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-70500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-59500</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-451200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-227100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-244300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-225500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>109800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-274300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-246500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-209800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-233000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-210100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-616400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-153300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-101800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-212700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-608500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-115400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-366700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>744400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-398000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-253300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-278400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>86700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>302600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1209600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-217200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>558200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-891800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>86300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-263800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>64400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-207400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-233700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-20000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>42000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-21300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>60800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-30400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>51300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>8600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>17800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-46700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-21400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>16700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>16400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>20000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-39100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-383600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-454500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>811400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-52700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-50400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-866300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>778000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-211000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-418600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-867500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>775300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>152500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>325600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-492700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>881200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>543300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-468500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>359800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>671700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-92900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-43900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1192500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1373800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-104100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-197700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>89700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>48100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-320600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>205300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>219700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>IPG</t>
   </si>
@@ -656,335 +656,342 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2710000</v>
+        <v>2242700</v>
       </c>
       <c r="E8" s="3">
-        <v>2495900</v>
+        <v>2327100</v>
       </c>
       <c r="F8" s="3">
-        <v>3023300</v>
+        <v>2182900</v>
       </c>
       <c r="G8" s="3">
-        <v>2678500</v>
+        <v>2586200</v>
       </c>
       <c r="H8" s="3">
-        <v>2666500</v>
+        <v>2309000</v>
       </c>
       <c r="I8" s="3">
-        <v>2521000</v>
+        <v>2328500</v>
       </c>
       <c r="J8" s="3">
+        <v>2176900</v>
+      </c>
+      <c r="K8" s="3">
         <v>2985900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2637700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2735700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2568500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2932100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2542000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2509600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2257000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2550000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2125500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2025700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2359800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2901800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2438100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2520200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2361200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2856000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2297500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2391800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2169100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2589800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2208200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2185800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2063800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2264500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1922200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2298900</v>
+        <v>1793400</v>
       </c>
       <c r="E9" s="3">
-        <v>2207900</v>
+        <v>1918100</v>
       </c>
       <c r="F9" s="3">
-        <v>2326900</v>
+        <v>1897200</v>
       </c>
       <c r="G9" s="3">
-        <v>2219400</v>
+        <v>1638300</v>
       </c>
       <c r="H9" s="3">
-        <v>2277100</v>
+        <v>1851500</v>
       </c>
       <c r="I9" s="3">
-        <v>2251700</v>
+        <v>1940600</v>
       </c>
       <c r="J9" s="3">
+        <v>1909400</v>
+      </c>
+      <c r="K9" s="3">
         <v>2337600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2216200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2300200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2229100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2354200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2092400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2025900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1915300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1976600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1748700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1795400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2188700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2320600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2079000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2162800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2166700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2247000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1970200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2069800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2049200</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>5</v>
@@ -1001,91 +1008,94 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>411100</v>
+        <v>449300</v>
       </c>
       <c r="E10" s="3">
-        <v>288000</v>
+        <v>409000</v>
       </c>
       <c r="F10" s="3">
-        <v>696400</v>
+        <v>285700</v>
       </c>
       <c r="G10" s="3">
-        <v>459100</v>
+        <v>947900</v>
       </c>
       <c r="H10" s="3">
-        <v>389400</v>
+        <v>457500</v>
       </c>
       <c r="I10" s="3">
-        <v>269300</v>
+        <v>387900</v>
       </c>
       <c r="J10" s="3">
+        <v>267500</v>
+      </c>
+      <c r="K10" s="3">
         <v>648300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>421500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>435500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>339400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>577900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>449600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>483700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>341700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>573400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>376800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>230300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>171100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>581200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>359100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>357400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>194500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>609000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>327300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>322000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>119900</v>
-      </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,210 +1358,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>234300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7400</v>
       </c>
-      <c r="F14" s="3">
-        <v>-36000</v>
-      </c>
       <c r="G14" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="H14" s="3">
         <v>11500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>109000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>87800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>269100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>55900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>132500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>7700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>40400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>11900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>19800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>24400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>8700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>13100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>25100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E15" s="3">
         <v>65000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>65200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>65300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>66000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>66500</v>
       </c>
       <c r="I15" s="3">
         <v>66500</v>
       </c>
       <c r="J15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="K15" s="3">
         <v>72100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>67000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>67100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>67800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>75100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>69400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>70100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>69200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>73700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>71000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>73100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>72800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>65400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>69000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>73000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>71100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>68900</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>44000</v>
       </c>
       <c r="AB15" s="3">
         <v>44000</v>
       </c>
       <c r="AC15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>46000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>32600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>42200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>41300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AI15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2389700</v>
+        <v>1879500</v>
       </c>
       <c r="E17" s="3">
-        <v>2318500</v>
+        <v>2010700</v>
       </c>
       <c r="F17" s="3">
-        <v>2379700</v>
+        <v>2000400</v>
       </c>
       <c r="G17" s="3">
-        <v>2313800</v>
+        <v>1977000</v>
       </c>
       <c r="H17" s="3">
-        <v>2358400</v>
+        <v>1934400</v>
       </c>
       <c r="I17" s="3">
-        <v>2336900</v>
+        <v>2021000</v>
       </c>
       <c r="J17" s="3">
+        <v>1988800</v>
+      </c>
+      <c r="K17" s="3">
         <v>2548600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2292800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2387300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2329200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2475600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2194900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2126900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2341800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1885500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2005100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2307200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2434400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2165500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2259200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2319600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2408800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2041600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2162400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2154700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2170000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1961900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1973200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2028200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1804500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1711100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>320300</v>
+        <v>363200</v>
       </c>
       <c r="E18" s="3">
-        <v>177400</v>
+        <v>316400</v>
       </c>
       <c r="F18" s="3">
-        <v>643600</v>
+        <v>182500</v>
       </c>
       <c r="G18" s="3">
-        <v>364700</v>
+        <v>609200</v>
       </c>
       <c r="H18" s="3">
-        <v>308100</v>
+        <v>374600</v>
       </c>
       <c r="I18" s="3">
-        <v>184100</v>
+        <v>307500</v>
       </c>
       <c r="J18" s="3">
+        <v>188100</v>
+      </c>
+      <c r="K18" s="3">
         <v>437300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>344900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>348400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>239300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>456500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>347100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>382700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>156500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>208200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>240000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>52600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>467400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>272600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>261000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>41600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>447200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>255900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>229400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>419800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>246300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>212600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>35600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>460000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>211100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>33300</v>
+        <v>-1300</v>
       </c>
       <c r="E20" s="3">
-        <v>46000</v>
+        <v>1700</v>
       </c>
       <c r="F20" s="3">
-        <v>41700</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>33500</v>
+        <v>-2300</v>
       </c>
       <c r="H20" s="3">
-        <v>33700</v>
+        <v>2300</v>
       </c>
       <c r="I20" s="3">
-        <v>37700</v>
+        <v>-400</v>
       </c>
       <c r="J20" s="3">
+        <v>800</v>
+      </c>
+      <c r="K20" s="3">
         <v>24900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>31400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>8600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>6100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>8200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>418600</v>
+        <v>429800</v>
       </c>
       <c r="E21" s="3">
-        <v>288600</v>
+        <v>379700</v>
       </c>
       <c r="F21" s="3">
-        <v>750600</v>
+        <v>247600</v>
       </c>
       <c r="G21" s="3">
-        <v>464200</v>
+        <v>676800</v>
       </c>
       <c r="H21" s="3">
-        <v>408300</v>
+        <v>438300</v>
       </c>
       <c r="I21" s="3">
-        <v>288300</v>
+        <v>374400</v>
       </c>
       <c r="J21" s="3">
+        <v>253800</v>
+      </c>
+      <c r="K21" s="3">
         <v>534300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>443300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>422900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>317100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>546400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>430600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>466800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>235200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>294100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>314400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>98000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>137600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>541400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>351400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>341100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>122200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>522200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>295700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>281600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>64400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>459300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>291400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>256300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>81700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>505600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>257700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E22" s="3">
         <v>57900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>62800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>61400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>58700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>63200</v>
       </c>
       <c r="I22" s="3">
         <v>55800</v>
       </c>
       <c r="J22" s="3">
+        <v>49700</v>
+      </c>
+      <c r="K22" s="3">
         <v>49400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>44900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>41000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>38000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>42900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>42600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>49600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>46800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>49800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>44800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>48200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>49700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>51600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>49800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>27600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>26100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>21000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>20900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>295700</v>
+        <v>109500</v>
       </c>
       <c r="E23" s="3">
-        <v>160600</v>
+        <v>295200</v>
       </c>
       <c r="F23" s="3">
-        <v>623900</v>
+        <v>160900</v>
       </c>
       <c r="G23" s="3">
-        <v>339500</v>
+        <v>626900</v>
       </c>
       <c r="H23" s="3">
-        <v>278600</v>
+        <v>337200</v>
       </c>
       <c r="I23" s="3">
-        <v>166000</v>
+        <v>279300</v>
       </c>
       <c r="J23" s="3">
+        <v>165900</v>
+      </c>
+      <c r="K23" s="3">
         <v>412800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>331400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>314800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>209900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>433300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>318300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>354100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>116400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>173600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>192600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-24900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>427800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>232700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>216500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>403900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>224100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>211500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>403500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>228200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>189300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>19800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>441100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E24" s="3">
         <v>75600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>47300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>155300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>91500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>33800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>109200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>76400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>83700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>49100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>67400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>73900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>86700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>58100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-86300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>86100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>64600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>43600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>62200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>60700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>63600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>135100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>54900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>81600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>106100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>220100</v>
+        <v>24200</v>
       </c>
       <c r="E26" s="3">
-        <v>113300</v>
+        <v>219600</v>
       </c>
       <c r="F26" s="3">
-        <v>468600</v>
+        <v>113600</v>
       </c>
       <c r="G26" s="3">
-        <v>248000</v>
+        <v>471600</v>
       </c>
       <c r="H26" s="3">
-        <v>268000</v>
+        <v>245700</v>
       </c>
       <c r="I26" s="3">
-        <v>132200</v>
+        <v>268700</v>
       </c>
       <c r="J26" s="3">
+        <v>132100</v>
+      </c>
+      <c r="K26" s="3">
         <v>303600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>255000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>231100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>160800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>365900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>244400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>267400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>92600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>115500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>278900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-43900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>341700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>168100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>172900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>341700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>163400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>147900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>268400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>173300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>107700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>335000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E27" s="3">
         <v>214500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>110400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>463200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>243700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>265500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>126000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>297200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>251800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>229600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>159400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>357900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>239900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>263300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>91700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>112300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>279700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-45600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>328900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>165600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>169500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>326200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>161000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>145800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>252300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>169700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>107700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>24700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>317600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,8 +2851,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2808,11 +2869,11 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>36000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-33300</v>
+        <v>1300</v>
       </c>
       <c r="E32" s="3">
-        <v>-46000</v>
+        <v>-1700</v>
       </c>
       <c r="F32" s="3">
-        <v>-41700</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-33500</v>
+        <v>2300</v>
       </c>
       <c r="H32" s="3">
-        <v>-33700</v>
+        <v>-2300</v>
       </c>
       <c r="I32" s="3">
-        <v>-37700</v>
+        <v>400</v>
       </c>
       <c r="J32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-24900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-31400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-8600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E33" s="3">
         <v>214500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>110400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>463200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>243700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>265500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>126000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>297200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>251800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>229600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>159400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>357900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>239900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>263300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>91700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>112300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>279700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-45600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>328900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>165600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>169500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>326200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>161000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>145800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>288300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>169700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>107700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>24700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>317600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E35" s="3">
         <v>214500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>110400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>463200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>243700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>265500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>126000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>297200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>251800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>229600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>159400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>357900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>239900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>263300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>91700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>112300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>279700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-45600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>328900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>165600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>169500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>326200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>161000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>145800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>288300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>169700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>107700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>24700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>317600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,132 +3698,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1532000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1545500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1931200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2386100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1574900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1628100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1678100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2545300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1768300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1983400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2402300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3270000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2490000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2340600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2015300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2509000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1628000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1085400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1554000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1192200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>520500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>614000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>630500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>673400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1860200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>493200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>597300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>790900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>704900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>657600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>775000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1097600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>891600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>5</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>101800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>102800</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>5</v>
@@ -3751,8 +3841,8 @@
       <c r="N42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -3796,150 +3886,156 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
+      <c r="AD42" s="3">
+        <v>0</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>3200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3100</v>
-      </c>
-      <c r="AH42" s="3">
-        <v>3000</v>
       </c>
       <c r="AI42" s="3">
         <v>3000</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>3000</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6930700</v>
+      </c>
+      <c r="E43" s="3">
         <v>6669800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6474600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7998000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6464300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6385900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5946500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7339000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6279100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6247900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6335200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7524900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6192900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5937000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5283000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6467100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5114600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4610300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5575500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7143300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6066500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6367100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6104900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7027200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6005000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6193500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5923600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6332400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5438400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5482900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5384200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5907800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5558100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,233 +4112,242 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>610300</v>
+        <v>321000</v>
       </c>
       <c r="E45" s="3">
-        <v>620100</v>
+        <v>83000</v>
       </c>
       <c r="F45" s="3">
-        <v>566300</v>
+        <v>95800</v>
       </c>
       <c r="G45" s="3">
-        <v>504400</v>
+        <v>150500</v>
       </c>
       <c r="H45" s="3">
-        <v>524200</v>
+        <v>83700</v>
       </c>
       <c r="I45" s="3">
+        <v>67300</v>
+      </c>
+      <c r="J45" s="3">
         <v>546300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>440900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>487500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>529500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>532500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>436900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>450000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>504900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>471900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>391500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>541700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>518600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>467200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>435200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>463000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>494300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>511600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>482300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>465300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>458900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>442600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>352200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>320500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>342800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>427200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>429600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9257700</v>
+      </c>
+      <c r="E46" s="3">
         <v>8825600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9025900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10950400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8645400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8641000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8170900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10325200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8534900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8760800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9270000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11231800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9132900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8782500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7770200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9367600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7284300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6214300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7596700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8770700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7050000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7475400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7247000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8182900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8330500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7145600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6963500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7475500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6463800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6486500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6589500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7438000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6733200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,210 +4424,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1659100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1713100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1755100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1799300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1809700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1870300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1879400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1914900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2024500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2088000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2161400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2220200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2182800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1994500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2028200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2069600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2260000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2153600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2278200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2352500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2331700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2363600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2122600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>790900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>602900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>602000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>634200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2337000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>637500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>635000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>616300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>622000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>581600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5421200</v>
+      </c>
+      <c r="E49" s="3">
         <v>5760600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5786000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5824500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5818600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5864300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5859300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5868700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5578300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5655000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5724600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5756200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5784100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5837000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5847900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5879100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5824700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5810500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5817200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5908700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5879700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5936100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5959700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5970700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3784700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3788100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3820400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3753100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3703500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3674400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3715300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>712500</v>
+        <v>477700</v>
       </c>
       <c r="E52" s="3">
-        <v>719100</v>
+        <v>459100</v>
       </c>
       <c r="F52" s="3">
-        <v>693100</v>
+        <v>441600</v>
       </c>
       <c r="G52" s="3">
-        <v>753600</v>
+        <v>428100</v>
       </c>
       <c r="H52" s="3">
-        <v>734400</v>
+        <v>464400</v>
       </c>
       <c r="I52" s="3">
-        <v>754500</v>
+        <v>447400</v>
       </c>
       <c r="J52" s="3">
+        <v>470300</v>
+      </c>
+      <c r="K52" s="3">
         <v>736200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>737500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>745400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>724900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>701000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>705500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>707700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>703400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>726400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>705700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>718500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>736800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>720000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>736200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>751800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>720700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>675800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>795000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>821900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>802700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>758400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>814900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>803600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>788600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>750800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>809400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17083200</v>
+      </c>
+      <c r="E54" s="3">
         <v>17011800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17286100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19267300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17027300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17110000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16664100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18845000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16875200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17249200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17880900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19909200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17805300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17321700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16349700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18042700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16074700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14896900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16428900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17751900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15997600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16526900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16050000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15620300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13513100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12357600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12240100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12704700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11716100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11678200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11697900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12485200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11839500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7061600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6909300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6729700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8355000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6448400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6573200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6460600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8235300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6535600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6861300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7245300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8960000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6844200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6605900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5862000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7269700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5105900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4328100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5559500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7205400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5656000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6022300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5733700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6698100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5515100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5738800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5467100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6420200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5561100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5872000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5672600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6303600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6025900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20600</v>
+        <v>266100</v>
       </c>
       <c r="E58" s="3">
-        <v>272100</v>
+        <v>267200</v>
       </c>
       <c r="F58" s="3">
-        <v>284300</v>
+        <v>520000</v>
       </c>
       <c r="G58" s="3">
-        <v>281000</v>
+        <v>536900</v>
       </c>
       <c r="H58" s="3">
-        <v>280500</v>
+        <v>529700</v>
       </c>
       <c r="I58" s="3">
-        <v>28300</v>
+        <v>524000</v>
       </c>
       <c r="J58" s="3">
+        <v>262900</v>
+      </c>
+      <c r="K58" s="3">
         <v>44900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>56400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>48200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>544500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>559800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>545900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>550500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>552900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>554900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>812600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>554400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>248100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>207400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>272500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>73800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>82700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>757700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>801500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>86900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>813700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>539400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>634900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>409600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1357400</v>
+        <v>639400</v>
       </c>
       <c r="E59" s="3">
-        <v>1496500</v>
+        <v>641000</v>
       </c>
       <c r="F59" s="3">
-        <v>1691600</v>
+        <v>766200</v>
       </c>
       <c r="G59" s="3">
-        <v>1596800</v>
+        <v>793500</v>
       </c>
       <c r="H59" s="3">
+        <v>753400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>721400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>734300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1703000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1577200</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1555100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1649200</v>
+      </c>
+      <c r="O59" s="3">
+        <v>1881800</v>
+      </c>
+      <c r="P59" s="3">
+        <v>1660300</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>1631000</v>
+      </c>
+      <c r="R59" s="3">
+        <v>1576600</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1760300</v>
+      </c>
+      <c r="T59" s="3">
+        <v>1569100</v>
+      </c>
+      <c r="U59" s="3">
+        <v>1483500</v>
+      </c>
+      <c r="V59" s="3">
+        <v>1423800</v>
+      </c>
+      <c r="W59" s="3">
+        <v>1660600</v>
+      </c>
+      <c r="X59" s="3">
+        <v>1494300</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1501600</v>
       </c>
-      <c r="I59" s="3">
-        <v>1471100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1703000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1577200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1555100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1649200</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1881800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1660300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1631000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1576600</v>
-      </c>
-      <c r="R59" s="3">
-        <v>1760300</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1569100</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1483500</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1423800</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1660600</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1494300</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1501600</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1524900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1352000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1093900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1088800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1053900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1168200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>571500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>534800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>683200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>992800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>631700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8465600</v>
+      </c>
+      <c r="E60" s="3">
         <v>8287300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8498300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10330900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8326200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8355300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7960000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9983200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8169200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8462700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8954200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10890000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9049000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8796700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7984500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9580500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7227900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6366500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7795900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9420400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7398400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7731300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7531100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8123900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6691700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7585300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7322500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7675300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6946300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6946200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6990700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7706000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6815100</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2918800</v>
+        <v>4016400</v>
       </c>
       <c r="E61" s="3">
-        <v>2918400</v>
+        <v>4064400</v>
       </c>
       <c r="F61" s="3">
-        <v>2917500</v>
+        <v>4099800</v>
       </c>
       <c r="G61" s="3">
-        <v>2916200</v>
+        <v>4134300</v>
       </c>
       <c r="H61" s="3">
-        <v>2915400</v>
+        <v>4163200</v>
       </c>
       <c r="I61" s="3">
-        <v>2871500</v>
+        <v>4232300</v>
       </c>
       <c r="J61" s="3">
+        <v>4213400</v>
+      </c>
+      <c r="K61" s="3">
         <v>2870700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2902500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2906100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2908100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2908600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2908300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2907900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2906900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2915800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3411300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3411700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3410900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2771900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3367100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3563800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3663700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3660200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3261400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1282700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1288200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1285600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1285000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1283100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1281900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1280700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1583300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1867900</v>
+        <v>770900</v>
       </c>
       <c r="E62" s="3">
-        <v>1950300</v>
+        <v>722300</v>
       </c>
       <c r="F62" s="3">
-        <v>1972800</v>
+        <v>768900</v>
       </c>
       <c r="G62" s="3">
-        <v>2007200</v>
+        <v>469500</v>
       </c>
       <c r="H62" s="3">
-        <v>2048000</v>
+        <v>760200</v>
       </c>
       <c r="I62" s="3">
-        <v>2174200</v>
+        <v>731100</v>
       </c>
       <c r="J62" s="3">
+        <v>832300</v>
+      </c>
+      <c r="K62" s="3">
         <v>2246800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2337300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2382000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2461900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2505800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2554100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2433600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2451500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2509400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2522100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2472400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2492100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2569300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2543600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2585100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2338800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1235500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1230100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1232200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1242200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1245400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1206600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1193200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1187700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1189000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1218700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13176200</v>
+        <v>13252900</v>
       </c>
       <c r="E66" s="3">
-        <v>13462000</v>
+        <v>13074000</v>
       </c>
       <c r="F66" s="3">
-        <v>15324700</v>
+        <v>13367000</v>
       </c>
       <c r="G66" s="3">
-        <v>13347100</v>
+        <v>15221200</v>
       </c>
       <c r="H66" s="3">
-        <v>13423700</v>
+        <v>13249600</v>
       </c>
       <c r="I66" s="3">
-        <v>13104800</v>
+        <v>13318700</v>
       </c>
       <c r="J66" s="3">
+        <v>13005700</v>
+      </c>
+      <c r="K66" s="3">
         <v>15197100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13470600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13812500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14393900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16383200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14633900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14258800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13475700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15147700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13352100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12446500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13896400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14976000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13528600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14103000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13734700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13227100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11375200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10295900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10131600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10493200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9702700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9695700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9734900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>10468100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9898100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4219600</v>
+      </c>
+      <c r="E72" s="3">
         <v>4325100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4239100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4254500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3911100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3782800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3638100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3632100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3449900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3311800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3196700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3154300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2908900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2777500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2623100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2636900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2623400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2444300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2591100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2689900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2455500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2381800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2303100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2400100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2158400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2076700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2010500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2104500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1849800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1774900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1751200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1804300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1546600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3725800</v>
+      </c>
+      <c r="E76" s="3">
         <v>3835600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3824100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3942600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3680200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3686300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3559300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3647900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3404600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3436700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3487000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3526000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3171400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3062900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2874000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2895000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2722600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2450400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2532500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2775900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2469000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2423900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2315300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2393200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2137900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2061700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2108500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2211500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2013400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1982500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1963000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2017100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1941400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E81" s="3">
         <v>214500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>110400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>463200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>243700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>265500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>126000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>297200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>251800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>229600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>159400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>357900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>239900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>263300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>91700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>112300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>279700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-45600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>328900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>165600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>169500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>326200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>161000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>145800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>288300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>169700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>107700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>24700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>317600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>65000</v>
+        <v>45000</v>
       </c>
       <c r="E83" s="3">
-        <v>65200</v>
+        <v>45300</v>
       </c>
       <c r="F83" s="3">
-        <v>65300</v>
+        <v>45600</v>
       </c>
       <c r="G83" s="3">
-        <v>66000</v>
+        <v>50000</v>
       </c>
       <c r="H83" s="3">
-        <v>66500</v>
+        <v>46800</v>
       </c>
       <c r="I83" s="3">
-        <v>66500</v>
+        <v>46000</v>
       </c>
       <c r="J83" s="3">
+        <v>46500</v>
+      </c>
+      <c r="K83" s="3">
         <v>72100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>67100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>67800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>75100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>69400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>70100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>69200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>73700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>71000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>73100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>72800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>65400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>69000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>73000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>71100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>68900</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>44000</v>
       </c>
       <c r="AB83" s="3">
         <v>44000</v>
       </c>
       <c r="AC83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AD83" s="3">
         <v>46000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>32600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>42200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>42700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>223800</v>
+      </c>
+      <c r="E89" s="3">
         <v>120700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-157400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>894800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>242700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-547600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1267600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>65600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-90800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-633600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1467000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>390200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>468200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-249800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1522100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>689300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-87100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-277100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1105600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>224600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>292500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-93500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>891800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>231000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>172200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-729900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1020800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>14100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>218700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-371800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>540300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>527700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-34800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-46400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-32900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-71900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-33800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-28300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-55500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-40100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-44600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-64700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-53700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-47300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-32800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-71400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>28300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-40400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-50000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>118900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-48600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-121000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-34700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-303900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-70200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-72000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-43300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-83700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-39200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-32500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-60800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-41000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-42800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-47200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2374900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-44500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-33200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-96400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-123900</v>
+        <v>123200</v>
       </c>
       <c r="E96" s="3">
-        <v>-126600</v>
+        <v>123900</v>
       </c>
       <c r="F96" s="3">
-        <v>-117900</v>
+        <v>126600</v>
       </c>
       <c r="G96" s="3">
-        <v>-118600</v>
+        <v>117900</v>
       </c>
       <c r="H96" s="3">
-        <v>-119400</v>
+        <v>118600</v>
       </c>
       <c r="I96" s="3">
-        <v>-123200</v>
+        <v>119400</v>
       </c>
       <c r="J96" s="3">
+        <v>123200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-112200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-113000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-113800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-118300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-106300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-106200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-106100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-109100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-99500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-99400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-99200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-100000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-90900</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-90800</v>
       </c>
       <c r="X96" s="3">
         <v>-90800</v>
       </c>
       <c r="Y96" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-90600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-80500</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-80400</v>
       </c>
       <c r="AB96" s="3">
         <v>-80400</v>
       </c>
       <c r="AC96" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-69100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-69800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-70500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-59500</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-219300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-451200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-227100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-244300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-225500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>109800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-274300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-246500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-209800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-233000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-210100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-616400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-153300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-101800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-212700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-608500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-115400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-366700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>744400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-398000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-253300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-278400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>86700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>302600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1209600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-217200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>558200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-891800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>86300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-263800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>64400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-207400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-233700</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-12700</v>
+        <v>-21300</v>
       </c>
       <c r="E101" s="3">
-        <v>-20000</v>
+        <v>-4000</v>
       </c>
       <c r="F101" s="3">
-        <v>42000</v>
+        <v>-9700</v>
       </c>
       <c r="G101" s="3">
-        <v>-21300</v>
+        <v>27500</v>
       </c>
       <c r="H101" s="3">
-        <v>-4000</v>
+        <v>-30400</v>
       </c>
       <c r="I101" s="3">
-        <v>-9700</v>
+        <v>-33800</v>
       </c>
       <c r="J101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K101" s="3">
         <v>60800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-30400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-33800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-30400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>51300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>17800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-46700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-21400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>16700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-24600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>16400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>20000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-39100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-383600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-454500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>811400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-52700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-50400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-866300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>778000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-211000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-418600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-867500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>775300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>152500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>325600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-492700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>881200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>543300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-468500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>359800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>671700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-92900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-43900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1192500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1373800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-104100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-197700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>89700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>48100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-320600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>205300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>219700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>IPG</t>
   </si>
@@ -656,345 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2434900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2242700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2327100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2182900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2586200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2309000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2328500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2176900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2985900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2637700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2735700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2568500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2932100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2542000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2509600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2257000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2550000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2125500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2025700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2359800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2901800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2438100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2520200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2361200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2856000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2297500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2391800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2169100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2589800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2208200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2185800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2063800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2264500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1922200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1523600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1793400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1918100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1897200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1638300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1851500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1940600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1909400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2337600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2216200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2300200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2229100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2354200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2092400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2025900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1915300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1976600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1748700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1795400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2188700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2320600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2079000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2162800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2166700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2247000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1970200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2069800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2049200</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>5</v>
@@ -1011,94 +1017,97 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>911300</v>
+      </c>
+      <c r="E10" s="3">
         <v>449300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>409000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>285700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>947900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>457500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>387900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>267500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>648300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>421500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>435500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>339400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>577900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>449600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>483700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>341700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>573400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>376800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>230300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>171100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>581200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>359100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>357400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>194500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>609000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>327300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>322000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>119900</v>
-      </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>5</v>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,216 +1377,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E14" s="3">
         <v>234300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-33300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>109000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-8900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>87800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>269100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>55900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>132500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>23900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>7700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>40400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>11900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>19800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>24400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>8700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>13100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>25100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E15" s="3">
         <v>65300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>65000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>65200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>65300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>66000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>66500</v>
       </c>
       <c r="J15" s="3">
         <v>66500</v>
       </c>
       <c r="K15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="L15" s="3">
         <v>72100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>67000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>67100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>67800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>75100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>69400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>70100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>69200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>73700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>71000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>73100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>72800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>65400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>69000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>73000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>71100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>68900</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>44000</v>
       </c>
       <c r="AC15" s="3">
         <v>44000</v>
       </c>
       <c r="AD15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AE15" s="3">
         <v>46000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>32600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>42200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>41300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AI15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1863200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1879500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2010700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2000400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1977000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1934400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2021000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1988800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2548600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2292800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2387300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2329200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2475600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2194900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2126900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2100500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2341800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1885500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2005100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2307200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2434400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2165500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2259200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2319600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2408800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2041600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2162400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2154700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2170000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1961900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1973200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2028200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1804500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1711100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>571700</v>
+      </c>
+      <c r="E18" s="3">
         <v>363200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>316400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>182500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>609200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>374600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>307500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>188100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>437300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>344900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>348400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>239300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>456500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>347100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>382700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>156500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>208200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>240000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>52600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>467400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>272600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>261000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>41600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>447200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>255900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>229400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>419800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>246300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>212600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>35600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>460000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>211100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>24900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>31400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>12200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>8600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>9800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>633200</v>
+      </c>
+      <c r="E21" s="3">
         <v>429800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>379700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>247600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>676800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>438300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>374400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>253800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>534300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>443300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>422900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>317100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>546400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>430600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>466800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>235200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>294100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>314400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>98000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>137600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>541400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>351400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>341100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>122200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>522200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>295700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>281600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>64400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>459300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>291400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>256300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>81700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>505600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>257700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E22" s="3">
         <v>54900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>62800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>61400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>58700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>55800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>49700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>49400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>44900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>41000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>38000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>42900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>42600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>49600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>46800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>50800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>49800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>44800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>48200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>49700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>51600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>27600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>26100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>19900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>20900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>21800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>484000</v>
+      </c>
+      <c r="E23" s="3">
         <v>109500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>295200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>160900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>626900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>337200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>279300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>165900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>412800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>331400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>314800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>209900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>433300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>318300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>354100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>116400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>173600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>192600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-24900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>20000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>427800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>232700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>216500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>403900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>224100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>211500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>403500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>228200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>189300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>19800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>441100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>125700</v>
+      </c>
+      <c r="E24" s="3">
         <v>85300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>75600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>47300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>155300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>91500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>33800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>109200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>76400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>83700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>49100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>67400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>73900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>86700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>58100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-86300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>19000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>86100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>64600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>43600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>62200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>60700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>63600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>135100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>54900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>81600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>106100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>358300</v>
+      </c>
+      <c r="E26" s="3">
         <v>24200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>219600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>113600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>471600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>245700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>268700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>132100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>303600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>255000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>231100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>160800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>365900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>244400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>267400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>92600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>115500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>278900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-43900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>341700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>168100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>172900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>341700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>163400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>147900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>268400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>173300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>107700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>335000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>344500</v>
+      </c>
+      <c r="E27" s="3">
         <v>20100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>214500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>110400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>463200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>243700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>265500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>126000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>297200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>251800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>229600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>159400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>357900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>239900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>263300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>91700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>112300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>279700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-45600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>328900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>165600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>169500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>326200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>161000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>145800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>252300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>169700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>107700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>24700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>317600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,8 +2914,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2872,11 +2932,11 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>36000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-24900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-31400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-12200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-8600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>344500</v>
+      </c>
+      <c r="E33" s="3">
         <v>20100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>214500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>110400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>463200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>243700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>265500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>126000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>297200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>251800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>229600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>159400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>357900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>239900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>263300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>91700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>112300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>279700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-45600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>328900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>165600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>169500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>326200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>161000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>145800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>288300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>169700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>107700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>24700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>317600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>344500</v>
+      </c>
+      <c r="E35" s="3">
         <v>20100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>214500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>110400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>463200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>243700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>265500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>126000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>297200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>251800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>229600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>159400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>357900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>239900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>263300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>91700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>112300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>279700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-45600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>328900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>165600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>169500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>326200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>161000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>145800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>288300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>169700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>107700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>24700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>317600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2187100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1532000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1545500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1931200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2386100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1574900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1628100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1678100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2545300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1768300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1983400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2402300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3270000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2490000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2340600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2015300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2509000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1628000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1085400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1554000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1192200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>520500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>614000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>630500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>673400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1860200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>493200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>597300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>790900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>704900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>657600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>775000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1097600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>891600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3821,16 +3910,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>101800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>102800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>5</v>
@@ -3844,8 +3933,8 @@
       <c r="O42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3889,130 +3978,136 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
+      <c r="AE42" s="3">
+        <v>0</v>
       </c>
       <c r="AF42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>3200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3100</v>
-      </c>
-      <c r="AI42" s="3">
-        <v>3000</v>
       </c>
       <c r="AJ42" s="3">
         <v>3000</v>
       </c>
+      <c r="AK42" s="3">
+        <v>3000</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7738100</v>
+      </c>
+      <c r="E43" s="3">
         <v>6930700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6669800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6474600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7998000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6464300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6385900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5946500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7339000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6279100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6247900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6335200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7524900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6192900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5937000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5283000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6467100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5114600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4610300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5575500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7143300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6066500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6367100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6104900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7027200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6005000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6193500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5923600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6332400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5438400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5482900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5384200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5907800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5558100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,216 +4210,225 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E45" s="3">
         <v>321000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>83000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>95800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>150500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>83700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>67300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>546300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>440900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>487500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>529500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>532500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>436900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>450000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>504900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>471900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>391500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>541700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>518600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>467200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>435200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>463000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>494300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>511600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>482300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>465300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>458900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>442600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>352200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>320500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>342800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>427200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>429600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10606000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9257700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8825600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9025900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10950400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8645400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8641000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8170900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10325200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8534900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8760800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9270000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11231800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9132900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8782500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7770200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9367600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7284300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6214300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7596700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8770700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7050000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7475400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7247000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8182900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8330500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7145600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6963500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7475500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6463800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6486500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6589500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7438000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6733200</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,8 +4453,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4427,216 +4531,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1604600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1659100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1713100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1755100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1799300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1809700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1870300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1879400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1914900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2024500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2088000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2161400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2220200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2182800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1994500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2028200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2069600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2260000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2153600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2278200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2352500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2331700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2363600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2122600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>790900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>602900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>602000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>634200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2337000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>637500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>635000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>616300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>622000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>581600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5349300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5421200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5760600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5786000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5824500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5818600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5864300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5859300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5868700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5578300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5655000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5724600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5756200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5784100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5837000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5847900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5879100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5824700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5810500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5817200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5908700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5879700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5936100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5959700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5970700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3784700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3788100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3820400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3753100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3703500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3674400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3715300</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>516700</v>
+      </c>
+      <c r="E52" s="3">
         <v>477700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>459100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>441600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>428100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>464400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>447400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>470300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>736200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>737500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>745400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>724900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>701000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>705500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>707700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>703400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>726400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>705700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>718500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>736800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>720000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>736200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>751800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>720700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>675800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>795000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>821900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>802700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>758400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>814900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>803600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>788600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>750800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>809400</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18325800</v>
+      </c>
+      <c r="E54" s="3">
         <v>17083200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17011800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17286100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19267300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17027300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17110000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16664100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18845000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16875200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17249200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17880900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19909200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17805300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17321700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16349700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18042700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16074700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14896900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16428900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17751900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15997600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16526900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16050000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15620300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13513100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12357600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12240100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12704700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11716100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11678200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11697900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12485200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11839500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8286100</v>
+      </c>
+      <c r="E57" s="3">
         <v>7061600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6909300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6729700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8355000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6448400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6573200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6460600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8235300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6535600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6861300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7245300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8960000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6844200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6605900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5862000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7269700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5105900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4328100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5559500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7205400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5656000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6022300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5733700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6698100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5515100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5738800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5467100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6420200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5561100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5872000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5672600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6303600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6025900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>277800</v>
+      </c>
+      <c r="E58" s="3">
         <v>266100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>267200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>520000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>536900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>529700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>524000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>262900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>44900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>56400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>46300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>59700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>48200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>544500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>559800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>545900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>550500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>552900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>554900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>812600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>554400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>248100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>207400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>272500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>73800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>82700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>757700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>801500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>86900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>813700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>539400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>634900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>409600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>618500</v>
+      </c>
+      <c r="E59" s="3">
         <v>639400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>641000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>766200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>793500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>753400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>721400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>734300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1703000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1577200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1555100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1649200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1881800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1660300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1631000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1576600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1760300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1569100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1483500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1423800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1660600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1494300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1501600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1524900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1352000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1093900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1088800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1053900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1168200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>571500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>534800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>683200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>992800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>631700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9758000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8465600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8287300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8498300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10330900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8326200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8355300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7960000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9983200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8169200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8462700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8954200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10890000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9049000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8796700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7984500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9580500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7227900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6366500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7795900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9420400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7398400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7731300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7531100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8123900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6691700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7585300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7322500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7675300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6946300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6946200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6990700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7706000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6815100</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3976800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4016400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4064400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4099800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4134300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4163200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4232300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4213400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2870700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2902500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2906100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2908100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2908600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2908300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2907900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2906900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2915800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3411300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3411700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3410900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2771900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3367100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3563800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3663700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3660200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3261400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1282700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1288200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1285600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1285000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1283100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1281900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1280700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1583300</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>417400</v>
+      </c>
+      <c r="E62" s="3">
         <v>770900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>722300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>768900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>469500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>760200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>731100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>832300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2246800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2337300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2382000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2461900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2505800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2554100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2433600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2451500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2509400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2522100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2472400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2492100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2569300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2543600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2585100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2338800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1235500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1230100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1232200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1242200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1245400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1206600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1193200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1187700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1189000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1218700</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14415700</v>
+      </c>
+      <c r="E66" s="3">
         <v>13252900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13074000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13367000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15221200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13249600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13318700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13005700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15197100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13470600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13812500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14393900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16383200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14633900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14258800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13475700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15147700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13352100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12446500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13896400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14976000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13528600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14103000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13734700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13227100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11375200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10295900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10131600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10493200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9702700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9695700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9734900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>10468100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9898100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4440200</v>
+      </c>
+      <c r="E72" s="3">
         <v>4219600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4325100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4239100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4254500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3911100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3782800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3638100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3632100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3449900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3311800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3196700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3154300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2908900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2777500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2623100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2636900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2623400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2444300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2591100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2689900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2455500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2381800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2303100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2400100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2158400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2076700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2010500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2104500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1849800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1774900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1751200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1804300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1546600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3797400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3725800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3835600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3824100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3942600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3680200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3686300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3559300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3647900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3404600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3436700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3487000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3526000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3171400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3062900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2874000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2895000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2722600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2450400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2532500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2775900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2469000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2423900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2315300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2393200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2137900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2061700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2108500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2211500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2013400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1982500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1963000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2017100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1941400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>344500</v>
+      </c>
+      <c r="E81" s="3">
         <v>20100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>214500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>110400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>463200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>243700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>265500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>126000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>297200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>251800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>229600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>159400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>357900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>239900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>263300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>91700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>112300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>279700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-45600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>328900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>165600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>169500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>326200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>161000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>145800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>288300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>169700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>107700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>24700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>317600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E83" s="3">
         <v>45000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>50000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>67000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>67100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>75100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>69400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>70100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>69200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>73700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>71000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>73100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>72800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>65400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>69000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>73000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>71100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>68900</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>44000</v>
       </c>
       <c r="AC83" s="3">
         <v>44000</v>
       </c>
       <c r="AD83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AE83" s="3">
         <v>46000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>32600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>42200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>42700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>868100</v>
+      </c>
+      <c r="E89" s="3">
         <v>223800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>120700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-157400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>894800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>242700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-35200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-547600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1267600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>65600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-90800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-633600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1467000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>390200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>468200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-249800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1522100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>689300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-87100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-277100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1105600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>224600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>292500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-93500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>891800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>231000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>172200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-729900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1020800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>14100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>218700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-371800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>540300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>527700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-47800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-46200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-30700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-71900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-61300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-33800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-55500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-40100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-44600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-64700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-53700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-47300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-32800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-71400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>28300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-41400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-40400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-50000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>118900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-48600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-121000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-34700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-303900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-61000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-70200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-43300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-83700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-39200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-60800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-41000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-47200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-30700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2374900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-55700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-33200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-96400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,112 +9052,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E96" s="3">
         <v>123200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>123900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>126600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>117900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>118600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>119400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>123200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-112200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-113000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-113800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-118300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-106300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-106200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-106100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-109100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-99500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-99400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-99200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-100000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-90900</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-90800</v>
       </c>
       <c r="Y96" s="3">
         <v>-90800</v>
       </c>
       <c r="Z96" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-90600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-80500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-80400</v>
       </c>
       <c r="AC96" s="3">
         <v>-80400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-69100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-69800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-70500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-59500</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-122300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-219300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-451200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-227100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-244300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-225500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>109800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-274300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-246500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-209800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-233000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-210100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-616400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-153300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-101800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-212700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-608500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-115400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-366700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>744400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-398000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-253300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-278400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>86700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>302600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1209600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-217200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>558200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-891800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>86300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-263800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>64400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-207400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-233700</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>27500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-30400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-33800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>60800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-30400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-33800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-30400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>51300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>17800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-46700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-21400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>16700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-24600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>16400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>20000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-39100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>654700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-383600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-454500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>811400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-52700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-50400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-866300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>778000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-211000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-418600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-867500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>775300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>152500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>325600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-492700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>881200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>543300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-468500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>359800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>671700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-92900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1192500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1373800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-104100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-197700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>89700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>48100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-320600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>205300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>219700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>IPG</t>
   </si>
@@ -656,354 +656,361 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1996300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2434900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2242700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2327100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2182900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2586200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2309000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2328500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2176900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2985900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2637700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2735700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2568500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2932100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2542000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2509600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2257000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2550000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2125500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2025700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2359800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2901800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2438100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2520200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2361200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2856000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2297500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2391800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2169100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2589800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2208200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2185800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2063800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2264500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1922200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1736100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1523600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1793400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1918100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1897200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1638300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1851500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1940600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1909400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2337600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2216200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2300200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2229100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2354200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2092400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2025900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1915300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1976600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1748700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1795400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2188700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2320600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2079000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2162800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2166700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2247000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1970200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2069800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2049200</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>5</v>
@@ -1020,97 +1027,100 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>260200</v>
+      </c>
+      <c r="E10" s="3">
         <v>911300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>449300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>409000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>285700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>947900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>457500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>387900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>267500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>648300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>421500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>435500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>339400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>577900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>449600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>483700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>341700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>573400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>376800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>230300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>171100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>581200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>359100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>357400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>194500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>609000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>327300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>322000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>119900</v>
-      </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>5</v>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,222 +1397,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>239700</v>
+      </c>
+      <c r="E14" s="3">
         <v>63700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>234300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-33300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>109000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-8900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>87800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>269100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>55900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>132500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>23300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>11900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>19800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>24400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>8700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>13100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>25100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E15" s="3">
         <v>63400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>65300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>65000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>65200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>65300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>66000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>66500</v>
       </c>
       <c r="K15" s="3">
         <v>66500</v>
       </c>
       <c r="L15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="M15" s="3">
         <v>72100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>67000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>67100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>67800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>75100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>69400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>70100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>69200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>73700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>71000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>73100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>72800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>65400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>69000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>73000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>71100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>68900</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>44000</v>
       </c>
       <c r="AD15" s="3">
         <v>44000</v>
       </c>
       <c r="AE15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>46000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>32600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>42200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>41300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AK15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1837500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1863200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1879500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2010700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1977000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1934400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2021000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1988800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2548600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2292800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2387300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2329200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2475600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2194900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2126900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2341800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1885500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2005100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2307200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2434400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2165500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2259200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2319600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2408800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2041600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2162400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2154700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2170000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1961900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1973200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2028200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1804500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1711100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>158800</v>
+      </c>
+      <c r="E18" s="3">
         <v>571700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>363200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>316400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>182500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>609200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>374600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>307500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>188100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>437300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>344900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>348400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>239300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>456500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>347100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>382700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>156500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>208200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>240000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>52600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>467400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>272600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>261000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>41600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>447200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>255900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>229400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>419800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>246300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>212600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>35600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>460000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>211100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>24900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>10000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>8200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>6900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>221700</v>
+      </c>
+      <c r="E21" s="3">
         <v>633200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>429800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>379700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>247600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>676800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>438300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>374400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>253800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>534300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>443300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>422900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>317100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>546400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>430600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>466800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>235200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>294100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>314400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>98000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>137600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>541400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>351400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>341100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>122200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>522200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>295700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>281600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>64400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>459300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>291400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>256300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>81700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>505600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>257700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E22" s="3">
         <v>54300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>54900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>57900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>62800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>61400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>58700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>55800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>49700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>49400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>44900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>41000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>38000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>42900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>42600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>49600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>46800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>50800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>49800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>44800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>48200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>49700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>51600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>49400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>27600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>26100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>19900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>21000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>21800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-94500</v>
+      </c>
+      <c r="E23" s="3">
         <v>484000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>109500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>295200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>160900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>626900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>337200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>279300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>165900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>412800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>331400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>314800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>209900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>433300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>318300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>354100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>116400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>173600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>192600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-24900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>427800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>232700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>216500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>403900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>224100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>211500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>403500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>228200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>189300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>441100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E24" s="3">
         <v>125700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>85300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>75600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>47300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>155300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>91500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>109200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>76400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>83700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>49100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>67400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>73900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>86700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>58100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-86300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>19000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>86100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>64600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>43600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>10500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>62200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>60700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>63600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>135100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>54900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>81600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>106100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-85300</v>
+      </c>
+      <c r="E26" s="3">
         <v>358300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>219600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>113600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>471600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>245700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>268700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>132100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>303600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>255000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>231100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>160800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>365900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>244400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>267400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>92600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>115500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>278900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-43900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>341700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>168100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>172900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>341700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>163400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>147900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>268400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>173300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>107700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>20100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>335000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="E27" s="3">
         <v>344500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>214500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>110400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>463200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>243700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>265500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>126000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>297200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>251800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>229600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>159400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>357900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>239900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>263300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>91700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>112300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>279700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-45600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>328900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>165600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>169500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>326200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>161000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>145800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>252300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>169700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>107700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>317600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2917,8 +2978,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2935,11 +2996,11 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>36000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-24900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-10000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="E33" s="3">
         <v>344500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>214500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>110400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>463200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>243700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>265500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>126000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>297200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>251800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>229600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>159400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>357900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>239900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>263300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>91700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>112300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>279700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-45600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>328900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>165600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>169500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>326200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>161000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>145800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>288300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>169700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>107700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>317600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="E35" s="3">
         <v>344500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>214500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>110400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>463200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>243700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>265500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>126000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>297200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>251800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>229600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>159400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>357900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>239900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>263300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>91700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>112300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>279700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-45600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>328900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>165600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>169500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>326200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>161000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>145800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>288300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>169700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>107700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>317600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1869000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2187100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1532000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1545500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1931200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2386100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1574900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1628100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1678100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2545300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1768300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1983400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2402300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3270000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2490000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2340600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2015300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2509000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1628000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1085400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1554000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1192200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>520500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>614000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>630500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>673400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1860200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>493200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>597300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>790900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>704900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>657600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>775000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1097600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>891600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3913,16 +4003,16 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>101800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>102800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>5</v>
@@ -3936,8 +4026,8 @@
       <c r="P42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3981,133 +4071,139 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
+      <c r="AF42" s="3">
+        <v>0</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="3">
         <v>3200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3100</v>
-      </c>
-      <c r="AJ42" s="3">
-        <v>3000</v>
       </c>
       <c r="AK42" s="3">
         <v>3000</v>
       </c>
+      <c r="AL42" s="3">
+        <v>3000</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6807500</v>
+      </c>
+      <c r="E43" s="3">
         <v>7738100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6930700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6669800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6474600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7998000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6464300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6385900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5946500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7339000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6279100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6247900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6335200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7524900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6192900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5937000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5283000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6467100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5114600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4610300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5575500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7143300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6066500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6367100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6104900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7027200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6005000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6193500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5923600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6332400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5438400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5482900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5384200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5907800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5558100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,222 +4309,231 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E45" s="3">
         <v>128400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>321000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>83000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>95800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>150500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>83700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>67300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>546300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>440900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>487500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>529500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>532500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>436900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>450000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>504900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>471900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>391500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>541700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>518600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>467200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>435200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>463000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>494300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>511600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>482300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>465300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>458900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>442600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>352200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>320500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>342800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>427200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>429600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9426400</v>
+      </c>
+      <c r="E46" s="3">
         <v>10606000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9257700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8825600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9025900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10950400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8645400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8641000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8170900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10325200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8534900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8760800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9270000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11231800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9132900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8782500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7770200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9367600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7284300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6214300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7596700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8770700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7050000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7475400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7247000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8182900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8330500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7145600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6963500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7475500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6463800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6486500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6589500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7438000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6733200</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4456,8 +4561,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4534,222 +4639,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1472000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1604600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1659100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1713100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1755100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1799300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1809700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1870300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1879400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1914900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2024500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2088000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2161400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2220200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2182800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1994500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2028200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2069600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2260000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2153600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2278200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2352500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2331700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2363600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2122600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>790900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>602900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>602000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>634200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2337000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>637500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>635000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>616300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>622000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>581600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5421800</v>
+      </c>
+      <c r="E49" s="3">
         <v>5349300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5421200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5760600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5786000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5824500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5818600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5864300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5859300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5868700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5578300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5655000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5724600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5756200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5784100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5837000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5847900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5879100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5824700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5810500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5817200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5908700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5879700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5936100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5959700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5970700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3784700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3788100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3820400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3753100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3703500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3674400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3715300</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>532800</v>
+      </c>
+      <c r="E52" s="3">
         <v>516700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>477700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>459100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>441600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>428100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>464400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>447400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>470300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>736200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>737500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>745400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>724900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>701000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>705500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>707700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>703400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>726400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>705700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>718500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>736800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>720000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>736200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>751800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>720700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>675800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>795000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>821900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>802700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>758400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>814900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>803600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>788600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>750800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>809400</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17125500</v>
+      </c>
+      <c r="E54" s="3">
         <v>18325800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17083200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17011800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17286100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19267300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17027300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17110000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16664100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18845000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16875200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17249200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17880900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19909200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17805300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17321700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16349700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18042700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16074700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14896900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16428900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17751900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15997600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16526900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16050000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15620300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13513100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12357600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12240100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12704700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11716100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11678200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11697900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12485200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11839500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7406500</v>
+      </c>
+      <c r="E57" s="3">
         <v>8286100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7061600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6909300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6729700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8355000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6448400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6573200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6460600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8235300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6535600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6861300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7245300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8960000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6844200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6605900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5862000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7269700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5105900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4328100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5559500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7205400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5656000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6022300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5733700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6698100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5515100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5738800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5467100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6420200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5561100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5872000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5672600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6303600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6025900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>274500</v>
+      </c>
+      <c r="E58" s="3">
         <v>277800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>266100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>267200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>520000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>536900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>529700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>524000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>262900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>44900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>56400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>59700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>48200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>544500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>559800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>545900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>550500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>552900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>554900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>812600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>554400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>248100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>207400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>272500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>73800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>82700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>757700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>801500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>86900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>813700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>539400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>634900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>409600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>711100</v>
+      </c>
+      <c r="E59" s="3">
         <v>618500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>639400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>641000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>766200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>793500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>753400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>721400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>734300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1703000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1577200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1555100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1649200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1881800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1660300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1631000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1576600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1760300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1569100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1483500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1423800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1660600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1494300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1501600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1524900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1352000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1093900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1088800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1053900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1168200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>571500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>534800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>683200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>992800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>631700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8840800</v>
+      </c>
+      <c r="E60" s="3">
         <v>9758000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8465600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8287300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8498300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10330900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8326200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8355300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7960000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9983200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8169200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8462700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8954200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10890000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9049000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8796700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7984500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9580500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7227900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6366500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7795900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9420400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7398400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7731300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7531100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8123900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6691700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7585300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7322500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7675300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6946300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6946200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6990700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7706000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6815100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3931300</v>
+      </c>
+      <c r="E61" s="3">
         <v>3976800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4016400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4064400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4099800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4134300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4163200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4232300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4213400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2870700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2902500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2906100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2908100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2908600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2908300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2907900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2906900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2915800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3411300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3411700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3410900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2771900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3367100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3563800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3663700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3660200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3261400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1282700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1288200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1285600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1285000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1283100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1281900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1280700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1583300</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>659900</v>
+      </c>
+      <c r="E62" s="3">
         <v>417400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>770900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>722300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>768900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>469500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>760200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>731100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>832300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2246800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2337300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2382000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2461900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2505800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2554100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2433600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2451500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2509400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2522100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2472400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2492100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2569300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2543600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2585100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2338800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1235500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1230100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1232200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1242200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1245400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1206600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1193200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1187700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1189000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1218700</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13432000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14415700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13252900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13074000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13367000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15221200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13249600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13318700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13005700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15197100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13470600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13812500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14393900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16383200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14633900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14258800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13475700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15147700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13352100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12446500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13896400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14976000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13528600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14103000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13734700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13227100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11375200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10295900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10131600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10493200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9702700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9695700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9734900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>10468100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9898100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4230700</v>
+      </c>
+      <c r="E72" s="3">
         <v>4440200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4219600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4325100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4239100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4254500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3911100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3782800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3638100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3632100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3449900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3311800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3196700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3154300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2908900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2777500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2623100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2636900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2623400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2444300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2591100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2689900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2455500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2381800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2303100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2400100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2158400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2076700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2010500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2104500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1849800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1774900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1751200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1804300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1546600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3584100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3797400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3725800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3835600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3824100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3942600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3680200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3686300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3559300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3647900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3404600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3436700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3487000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3526000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3171400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3062900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2874000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2895000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2722600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2450400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2532500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2775900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2469000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2423900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2315300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2393200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2137900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2061700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2108500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2211500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2013400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1982500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1963000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2017100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1941400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="E81" s="3">
         <v>344500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>214500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>110400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>463200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>243700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>265500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>126000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>297200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>251800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>229600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>159400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>357900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>239900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>263300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>91700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>112300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>279700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-45600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>328900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>165600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>169500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>326200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>161000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>145800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>288300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>169700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>107700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>317600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E83" s="3">
         <v>44400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>50000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>72100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>67000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>67800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>75100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>69400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>70100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>69200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>73700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>71000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>73100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>72800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>65400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>69000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>73000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>71100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>68900</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>44000</v>
       </c>
       <c r="AD83" s="3">
         <v>44000</v>
       </c>
       <c r="AE83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>46000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>32600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>42200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>42700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E89" s="3">
         <v>868100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>223800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>120700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-157400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>894800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>242700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-547600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1267600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>65600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-90800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-633600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1467000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>390200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>468200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-249800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1522100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>689300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-87100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-277100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1105600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>224600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>292500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-93500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>891800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>231000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>172200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-729900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1020800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>14100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>218700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-371800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>540300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>527700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-34600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-37300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-52200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-47800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-71900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-61300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-33800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-55500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-40100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-44600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-64700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-53700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-32800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-71400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>28300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-41400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-40400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-50000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>118900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-48600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-121000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-303900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-61000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-70200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-72000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-43300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-83700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-39200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-32500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-60800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-47200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2374900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-55700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-44500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-33200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-96400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9286,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E96" s="3">
         <v>122800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>123200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>123900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>126600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>117900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>118600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>119400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>123200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-112200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-113000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-113800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-118300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-106300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-106200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-106100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-109100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-99500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-99400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-99200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-100000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-90900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-90800</v>
       </c>
       <c r="Z96" s="3">
         <v>-90800</v>
       </c>
       <c r="AA96" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-90600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-80500</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-80400</v>
       </c>
       <c r="AD96" s="3">
         <v>-80400</v>
       </c>
       <c r="AE96" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-69100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-69800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-70500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-59500</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-122300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-219300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-451200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-227100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-244300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-225500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>109800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-274300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-246500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-209800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-233000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-210100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-616400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-153300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-101800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-212700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-608500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-115400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-366700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>744400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-398000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-253300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-278400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>86700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>302600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1209600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-217200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>558200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-891800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>86300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-263800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>64400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-207400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-233700</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E101" s="3">
         <v>42000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-21300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>27500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-30400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-33800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>60800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-30400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-33800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-12400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-30400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>51300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>17800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-46700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-21400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>16700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-24600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-39100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-319800</v>
+      </c>
+      <c r="E102" s="3">
         <v>654700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-383600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-454500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>811400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-52700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-50400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-866300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>778000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-211000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-418600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-867500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>775300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>152500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>325600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-492700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>881200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>543300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-468500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>359800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>671700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-92900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1192500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1373800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-104100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-197700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>89700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>48100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-320600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>205300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>219700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>IPG</t>
   </si>
@@ -656,364 +656,371 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2172700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1996300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2434900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2242700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2327100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2182900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2586200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2309000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2328500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2176900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2985900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2637700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2735700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2568500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2932100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2542000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2509600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2257000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2550000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2125500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2025700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2359800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2901800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2438100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2520200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2361200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2856000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2297500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2391800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2169100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2589800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2208200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2185800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2063800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2264500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1922200</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1705700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1736100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1523600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1793400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1918100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1897200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1638300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1851500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1940600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1909400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2337600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2216200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2300200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2229100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2354200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2092400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2025900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1915300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1976600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1748700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1795400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2188700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2320600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2079000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2162800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2166700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2247000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1970200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2069800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2049200</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AH9" s="3" t="s">
         <v>5</v>
@@ -1030,100 +1037,103 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>467000</v>
+      </c>
+      <c r="E10" s="3">
         <v>260200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>911300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>449300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>409000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>285700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>947900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>457500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>387900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>267500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>648300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>421500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>435500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>339400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>577900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>449600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>483700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>341700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>573400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>376800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>230300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>171100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>581200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>359100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>357400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>194500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>609000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>327300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>322000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>119900</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AH10" s="3" t="s">
         <v>5</v>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,228 +1417,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E14" s="3">
         <v>239700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>63700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>234300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-33300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>109000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-8900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>87800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>269100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>55900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>132500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>23900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>40400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>11900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>24400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>8700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>13100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>25100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E15" s="3">
         <v>61000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>63400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>65300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>65000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>65200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>65300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>66000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>66500</v>
       </c>
       <c r="L15" s="3">
         <v>66500</v>
       </c>
       <c r="M15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="N15" s="3">
         <v>72100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>67000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>67100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>67800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>75100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>69400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>70100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>69200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>73700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>71000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>73100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>72800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>65400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>69000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>73000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>71100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>68900</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>44000</v>
       </c>
       <c r="AE15" s="3">
         <v>44000</v>
       </c>
       <c r="AF15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>46000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>32600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>42200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>41300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AK15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AL15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1802400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1837500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1863200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1879500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2010700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1977000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1934400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2021000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1988800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2548600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2292800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2387300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2329200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2475600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2194900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2126900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2100500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2341800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1885500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2005100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2307200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2434400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2165500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2259200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2319600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2408800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2041600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2162400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2154700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2170000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1961900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1973200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2028200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1804500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1711100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>370300</v>
+      </c>
+      <c r="E18" s="3">
         <v>158800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>571700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>363200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>316400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>182500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>609200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>374600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>307500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>188100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>437300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>344900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>348400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>239300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>456500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>347100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>382700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>156500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>208200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>240000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>52600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>467400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>272600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>261000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>41600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>447200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>255900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>229400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>419800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>246300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>212600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>35600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>460000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>211100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>24900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>31400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>9500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>8200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>430700</v>
+      </c>
+      <c r="E21" s="3">
         <v>221700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>633200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>429800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>379700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>247600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>676800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>438300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>374400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>253800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>534300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>443300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>422900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>317100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>546400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>430600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>466800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>235200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>294100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>314400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>98000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>137600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>541400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>351400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>341100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>122200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>522200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>295700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>281600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>64400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>459300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>291400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>256300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>81700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>505600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>257700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E22" s="3">
         <v>50100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>54300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>54900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>57900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>62800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>61400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>58700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>55800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>49700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>49400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>44900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>41000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>38000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>42900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>42600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>49600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>46800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>50800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>49800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>44800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>48200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>51600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>49800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>49400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>27600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>26100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>19900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>25700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>20900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>21800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>218200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-94500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>484000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>109500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>295200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>160900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>626900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>337200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>279300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>165900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>412800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>331400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>314800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>209900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>433300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>318300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>354100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>116400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>173600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>192600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-24900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>427800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>232700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>216500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>403900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>224100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>211500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>403500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>228200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>189300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>19800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>441100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-9200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>125700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>85300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>75600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>47300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>155300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>91500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>109200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>76400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>83700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>49100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>67400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>73900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>86700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>58100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-86300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>19000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>86100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>64600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>62200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>60700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>63600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>12700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>135100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>81600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>106100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-85300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>358300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>219600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>113600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>471600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>245700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>268700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>132100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>303600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>255000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>231100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>160800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>365900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>244400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>267400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>92600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>115500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>278900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-43900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>341700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>168100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>172900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>341700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>163400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>147900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>268400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>173300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>20100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>335000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-85400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>344500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>214500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>110400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>463200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>243700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>265500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>126000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>297200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>251800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>229600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>159400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>357900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>239900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>263300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>91700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>112300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>279700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-45600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>328900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>165600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>169500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>326200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>161000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>145800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>252300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>169700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>24700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>317600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2981,8 +3042,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2999,11 +3060,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>36000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-24900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-31400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-9500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-85400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>344500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>214500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>110400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>463200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>243700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>265500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>126000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>297200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>251800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>229600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>159400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>357900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>239900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>263300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>91700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>112300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>279700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-45600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>328900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>165600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>169500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>326200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>161000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>145800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>288300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>169700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>24700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>317600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-85400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>344500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>214500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>110400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>463200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>243700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>265500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>126000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>297200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>251800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>229600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>159400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>357900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>239900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>263300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>91700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>112300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>279700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-45600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>328900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>165600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>169500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>326200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>161000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>145800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>288300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>169700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>24700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>317600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1564400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1869000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2187100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1532000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1545500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1931200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2386100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1574900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1628100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1678100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2545300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1768300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1983400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2402300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3270000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2490000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2340600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2015300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2509000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1628000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1085400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1554000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1192200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>520500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>614000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>630500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>673400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1860200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>493200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>597300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>790900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>704900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>657600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>775000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1097600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>891600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4006,16 +4096,16 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>101800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>102800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>5</v>
@@ -4029,8 +4119,8 @@
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -4074,136 +4164,142 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
+      <c r="AG42" s="3">
+        <v>0</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3100</v>
-      </c>
-      <c r="AK42" s="3">
-        <v>3000</v>
       </c>
       <c r="AL42" s="3">
         <v>3000</v>
       </c>
+      <c r="AM42" s="3">
+        <v>3000</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6953700</v>
+      </c>
+      <c r="E43" s="3">
         <v>6807500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7738100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6930700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6669800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6474600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7998000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6464300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6385900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5946500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7339000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6279100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6247900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6335200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7524900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6192900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5937000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5283000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6467100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5114600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4610300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5575500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7143300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6066500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6367100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6104900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7027200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6005000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6193500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5923600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6332400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5438400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5482900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5384200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5907800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5558100</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,228 +4408,237 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E45" s="3">
         <v>79600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>128400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>321000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>83000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>95800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>150500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>83700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>67300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>546300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>440900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>487500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>529500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>532500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>436900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>450000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>504900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>471900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>391500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>541700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>518600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>467200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>435200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>463000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>494300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>511600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>482300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>465300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>458900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>442600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>352200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>320500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>342800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>427200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>429600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9301100</v>
+      </c>
+      <c r="E46" s="3">
         <v>9426400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10606000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9257700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8825600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9025900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10950400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8645400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8641000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8170900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10325200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8534900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8760800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9270000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11231800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9132900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8782500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7770200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9367600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7284300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6214300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7596700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8770700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7050000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7475400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7247000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8182900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8330500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7145600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6963500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7475500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6463800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6486500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6589500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7438000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6733200</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4642,228 +4747,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1472000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1604600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1659100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1713100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1755100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1799300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1809700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1870300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1879400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1914900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2024500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2088000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2161400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2220200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2182800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1994500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2028200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2069600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2260000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2153600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2278200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2352500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2331700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2363600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2122600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>790900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>602900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>602000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>634200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2337000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>637500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>635000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>616300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>622000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>581600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5444300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5421800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5349300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5421200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5760600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5786000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5824500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5818600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5864300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5859300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5868700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5578300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5655000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5724600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5756200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5784100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5837000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5847900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5879100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5824700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5810500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5817200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5908700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5879700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5936100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5959700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5970700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3784700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3788100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3820400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3753100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3703500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3674400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3715300</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E52" s="3">
         <v>532800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>516700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>477700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>459100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>441600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>428100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>464400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>447400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>470300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>736200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>737500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>745400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>724900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>701000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>705500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>707700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>703400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>726400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>705700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>718500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>736800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>720000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>736200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>751800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>720700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>675800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>795000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>821900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>802700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>758400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>814900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>803600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>788600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>750800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>809400</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17027100</v>
+      </c>
+      <c r="E54" s="3">
         <v>17125500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18325800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17083200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17011800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17286100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19267300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17027300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17110000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16664100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18845000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16875200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17249200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17880900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19909200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17805300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17321700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16349700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18042700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16074700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14896900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16428900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17751900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15997600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16526900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16050000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15620300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13513100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12357600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12240100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12704700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11716100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11678200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11697900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12485200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11839500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7185900</v>
+      </c>
+      <c r="E57" s="3">
         <v>7406500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8286100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7061600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6909300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6729700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8355000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6448400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6573200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6460600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8235300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6535600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6861300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7245300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8960000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6844200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6605900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5862000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7269700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5105900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4328100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5559500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7205400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5656000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6022300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5733700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6698100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5515100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5738800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5467100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6420200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5561100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5872000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5672600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6303600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6025900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>285600</v>
+      </c>
+      <c r="E58" s="3">
         <v>274500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>277800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>266100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>267200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>520000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>536900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>529700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>524000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>262900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>44900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>56400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>46300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>59700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>48200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>544500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>559800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>545900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>550500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>552900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>554900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>812600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>554400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>248100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>207400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>272500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>73800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>82700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>757700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>801500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>86900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>813700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>539400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>634900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>409600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>750900</v>
+      </c>
+      <c r="E59" s="3">
         <v>711100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>618500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>639400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>641000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>766200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>793500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>753400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>721400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>734300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1703000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1577200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1555100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1649200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1881800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1660300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1631000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1576600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1760300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1569100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1483500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1423800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1660600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1494300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1501600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1524900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1352000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1093900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1088800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1053900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1168200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>571500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>534800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>683200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>992800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>631700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8706400</v>
+      </c>
+      <c r="E60" s="3">
         <v>8840800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9758000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8465600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8287300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8498300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10330900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8326200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8355300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7960000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9983200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8169200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8462700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8954200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10890000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9049000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8796700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7984500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9580500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7227900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6366500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7795900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9420400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7398400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7731300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7531100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8123900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6691700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7585300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7322500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7675300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6946300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6946200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6990700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7706000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6815100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3899100</v>
+      </c>
+      <c r="E61" s="3">
         <v>3931300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3976800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4016400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4064400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4099800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4134300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4163200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4232300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4213400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2870700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2902500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2906100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2908100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2908600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2908300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2907900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2906900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2915800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3411300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3411700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3410900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2771900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3367100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3563800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3663700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3660200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3261400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1282700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1288200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1285600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1283100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1281900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1280700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1583300</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>636600</v>
+      </c>
+      <c r="E62" s="3">
         <v>659900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>417400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>770900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>722300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>768900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>469500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>760200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>731100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>832300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2246800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2337300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2382000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2461900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2505800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2554100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2433600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2451500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2509400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2522100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2472400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2492100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2569300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2543600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2585100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2338800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1235500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1230100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1232200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1242200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1245400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1206600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1193200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1187700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1189000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1218700</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13242100</v>
+      </c>
+      <c r="E66" s="3">
         <v>13432000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14415700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13252900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13074000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13367000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15221200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13249600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13318700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13005700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15197100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13470600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13812500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14393900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16383200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14633900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14258800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13475700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15147700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13352100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12446500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13896400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14976000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13528600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14103000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13734700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13227100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11375200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10295900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10131600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10493200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9702700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9695700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9734900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10468100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9898100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4294300</v>
+      </c>
+      <c r="E72" s="3">
         <v>4230700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4440200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4219600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4325100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4239100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4254500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3911100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3782800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3638100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3632100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3449900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3311800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3196700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3154300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2908900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2777500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2623100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2636900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2623400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2444300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2591100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2689900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2455500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2381800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2303100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2400100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2158400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2076700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2010500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2104500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1849800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1774900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1751200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1804300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1546600</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3712400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3584100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3797400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3725800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3835600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3824100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3942600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3680200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3686300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3559300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3647900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3404600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3436700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3487000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3526000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3171400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3062900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2874000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2895000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2722600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2450400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2532500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2775900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2469000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2423900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2315300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2393200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2137900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2061700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2108500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2211500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2013400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1982500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1963000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2017100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1941400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-85400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>344500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>214500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>110400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>463200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>243700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>265500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>126000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>297200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>251800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>229600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>159400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>357900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>239900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>263300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>91700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>112300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>279700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-45600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>328900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>165600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>169500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>326200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>161000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>145800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>288300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>169700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>24700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>317600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>128600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E83" s="3">
         <v>44500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>45600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>50000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>72100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>67100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>75100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>69400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>70100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>69200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>73700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>71000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>73100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>72800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>65400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>69000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>73000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>71100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>68900</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>44000</v>
       </c>
       <c r="AE83" s="3">
         <v>44000</v>
       </c>
       <c r="AF83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AG83" s="3">
         <v>46000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>32600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>42200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>41000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>42700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-37000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>868100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>223800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>120700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-157400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>894800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>242700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-547600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1267600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>65600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-90800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-633600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1467000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>390200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>468200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-249800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1522100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>689300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-87100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-277100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1105600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>224600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>292500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-93500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>891800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>231000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>172200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-729900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1020800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>14100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>218700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-371800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>540300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>527700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-34800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-35100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-52200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-46200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-71900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-61300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-33800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-55500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-40100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-44600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-64700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-53700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-32800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>28300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-50000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>118900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-48600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-121000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-303900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-61000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-70200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-72000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-43300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-83700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-39200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-32500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-60800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-47200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-30700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2374900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-55700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-33200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-96400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9520,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E96" s="3">
         <v>125300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>122800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>123200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>123900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>126600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>117900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>118600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>119400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>123200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-112200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-113000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-113800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-118300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-106300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-106200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-106100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-109100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-99500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-99400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-99200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-100000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-90900</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-90800</v>
       </c>
       <c r="AA96" s="3">
         <v>-90800</v>
       </c>
       <c r="AB96" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-90600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-80500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-80400</v>
       </c>
       <c r="AE96" s="3">
         <v>-80400</v>
       </c>
       <c r="AF96" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-69100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-69800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-70500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-59500</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-223200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-248000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-122300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-219300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-451200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-227100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-244300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-225500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>109800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-274300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-246500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-209800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-233000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-616400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-153300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-101800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-212700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-608500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-115400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-366700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>744400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-398000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-253300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-278400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>86700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>302600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1209600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-217200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>558200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-891800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>86300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-263800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>64400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-207400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-233700</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-20000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>42000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-21300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>27500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-30400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>60800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-30400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-33800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-30400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>51300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>8600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>17800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-46700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-21400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>16700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-24600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>16400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>20000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-39100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-319800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>654700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-383600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-454500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>811400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-52700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-50400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-866300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>778000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-211000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-418600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-867500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>775300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>152500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>325600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-492700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>881200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>543300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-468500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>359800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>671700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-92900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-16400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1192500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1373800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-104100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-197700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>89700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>48100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-320600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>205300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>219700</v>
       </c>
     </row>
